--- a/artfynd/A 46103-2025 artfynd.xlsx
+++ b/artfynd/A 46103-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AY36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128964083</v>
+        <v>128963916</v>
       </c>
       <c r="B2" t="n">
-        <v>91508</v>
+        <v>91473</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -717,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>776887</v>
+        <v>776921</v>
       </c>
       <c r="R2" t="n">
-        <v>7157655</v>
+        <v>7157641</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -780,41 +780,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128963916</v>
+        <v>128964143</v>
       </c>
       <c r="B3" t="n">
-        <v>91473</v>
+        <v>79124</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -822,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>776921</v>
+        <v>776873</v>
       </c>
       <c r="R3" t="n">
-        <v>7157641</v>
+        <v>7157628</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,6 +862,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>fertil!</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128964143</v>
+        <v>128964083</v>
       </c>
       <c r="B4" t="n">
-        <v>79124</v>
+        <v>91508</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -896,34 +905,30 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -931,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>776873</v>
+        <v>776887</v>
       </c>
       <c r="R4" t="n">
-        <v>7157628</v>
+        <v>7157655</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -967,11 +972,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-02</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>fertil!</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1104,7 +1104,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128963706</v>
+        <v>128964110</v>
       </c>
       <c r="B6" t="n">
         <v>91458</v>
@@ -1146,10 +1146,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>776952</v>
+        <v>776877</v>
       </c>
       <c r="R6" t="n">
-        <v>7157667</v>
+        <v>7157631</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1209,32 +1209,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128964270</v>
+        <v>128963706</v>
       </c>
       <c r="B7" t="n">
-        <v>91962</v>
+        <v>91458</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1209</v>
+        <v>112</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1251,10 +1251,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>776865</v>
+        <v>776952</v>
       </c>
       <c r="R7" t="n">
-        <v>7157670</v>
+        <v>7157667</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,32 +1314,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128964110</v>
+        <v>128964270</v>
       </c>
       <c r="B8" t="n">
-        <v>91458</v>
+        <v>91962</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>112</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1356,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>776877</v>
+        <v>776865</v>
       </c>
       <c r="R8" t="n">
-        <v>7157631</v>
+        <v>7157670</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -2046,10 +2046,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128964198</v>
+        <v>128964345</v>
       </c>
       <c r="B15" t="n">
-        <v>91508</v>
+        <v>79124</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2057,27 +2057,27 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -2088,10 +2088,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>776862</v>
+        <v>776870</v>
       </c>
       <c r="R15" t="n">
-        <v>7157681</v>
+        <v>7157667</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2151,10 +2151,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128964345</v>
+        <v>128964198</v>
       </c>
       <c r="B16" t="n">
-        <v>79124</v>
+        <v>91508</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2162,27 +2162,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -2193,10 +2193,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>776870</v>
+        <v>776862</v>
       </c>
       <c r="R16" t="n">
-        <v>7157667</v>
+        <v>7157681</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2256,42 +2256,42 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128963540</v>
+        <v>128964055</v>
       </c>
       <c r="B17" t="n">
-        <v>98636</v>
+        <v>57717</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2299,10 +2299,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>777003</v>
+        <v>776909</v>
       </c>
       <c r="R17" t="n">
-        <v>7157598</v>
+        <v>7157645</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2337,13 +2337,17 @@
           <t>2025-10-02</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>hack i låga</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2362,10 +2366,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128964055</v>
+        <v>128964180</v>
       </c>
       <c r="B18" t="n">
-        <v>57717</v>
+        <v>79124</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2373,31 +2377,30 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2405,10 +2408,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>776909</v>
+        <v>776839</v>
       </c>
       <c r="R18" t="n">
-        <v>7157645</v>
+        <v>7157679</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2443,17 +2446,13 @@
           <t>2025-10-02</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>hack i låga</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2472,38 +2471,38 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128964180</v>
+        <v>128963674</v>
       </c>
       <c r="B19" t="n">
-        <v>79124</v>
+        <v>91473</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -2514,10 +2513,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>776839</v>
+        <v>776962</v>
       </c>
       <c r="R19" t="n">
-        <v>7157679</v>
+        <v>7157631</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2577,41 +2576,42 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128963674</v>
+        <v>128963540</v>
       </c>
       <c r="B20" t="n">
-        <v>91473</v>
+        <v>98636</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2619,10 +2619,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>776962</v>
+        <v>777003</v>
       </c>
       <c r="R20" t="n">
-        <v>7157631</v>
+        <v>7157598</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3217,10 +3217,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128963472</v>
+        <v>128964193</v>
       </c>
       <c r="B26" t="n">
-        <v>98636</v>
+        <v>91962</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3228,31 +3228,30 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3260,10 +3259,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>777013</v>
+        <v>776862</v>
       </c>
       <c r="R26" t="n">
-        <v>7157601</v>
+        <v>7157681</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3296,11 +3295,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-02</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>ca 2 x 2 meter med bladrosetter!</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3328,10 +3322,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128964193</v>
+        <v>128963472</v>
       </c>
       <c r="B27" t="n">
-        <v>91962</v>
+        <v>98636</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3339,30 +3333,31 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3370,10 +3365,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>776862</v>
+        <v>777013</v>
       </c>
       <c r="R27" t="n">
-        <v>7157681</v>
+        <v>7157601</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3406,6 +3401,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>ca 2 x 2 meter med bladrosetter!</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3748,7 +3748,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128964019</v>
+        <v>128963102</v>
       </c>
       <c r="B31" t="n">
         <v>91508</v>
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>776903</v>
+        <v>776998</v>
       </c>
       <c r="R31" t="n">
-        <v>7157641</v>
+        <v>7157616</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3853,7 +3853,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128963102</v>
+        <v>128964019</v>
       </c>
       <c r="B32" t="n">
         <v>91508</v>
@@ -3895,10 +3895,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>776998</v>
+        <v>776903</v>
       </c>
       <c r="R32" t="n">
-        <v>7157616</v>
+        <v>7157641</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4066,6 +4066,321 @@
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>128974663</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79124</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Hösjöälven, Vb</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>776783</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7157582</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>128974745</v>
+      </c>
+      <c r="B35" t="n">
+        <v>91526</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Hösjöälven, Vb</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>776788</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7157582</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>128973835</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79124</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Hösjöälven, Vb</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>776636</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7157750</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 46103-2025 artfynd.xlsx
+++ b/artfynd/A 46103-2025 artfynd.xlsx
@@ -675,41 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128963916</v>
+        <v>128964143</v>
       </c>
       <c r="B2" t="n">
-        <v>91473</v>
+        <v>79124</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -717,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>776921</v>
+        <v>776873</v>
       </c>
       <c r="R2" t="n">
-        <v>7157641</v>
+        <v>7157628</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,6 +757,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>fertil!</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,45 +789,41 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128964143</v>
+        <v>128963916</v>
       </c>
       <c r="B3" t="n">
-        <v>79124</v>
+        <v>91473</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -826,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>776873</v>
+        <v>776921</v>
       </c>
       <c r="R3" t="n">
-        <v>7157628</v>
+        <v>7157641</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,11 +867,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-02</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>fertil!</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1945,10 +1945,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128963824</v>
+        <v>128964198</v>
       </c>
       <c r="B14" t="n">
-        <v>79124</v>
+        <v>91508</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1956,25 +1956,29 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
@@ -1983,10 +1987,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>776924</v>
+        <v>776862</v>
       </c>
       <c r="R14" t="n">
-        <v>7157645</v>
+        <v>7157681</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2046,7 +2050,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128964345</v>
+        <v>128963824</v>
       </c>
       <c r="B15" t="n">
         <v>79124</v>
@@ -2075,11 +2079,7 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
@@ -2088,10 +2088,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>776870</v>
+        <v>776924</v>
       </c>
       <c r="R15" t="n">
-        <v>7157667</v>
+        <v>7157645</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2151,10 +2151,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128964198</v>
+        <v>128964345</v>
       </c>
       <c r="B16" t="n">
-        <v>91508</v>
+        <v>79124</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2162,27 +2162,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -2193,10 +2193,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>776862</v>
+        <v>776870</v>
       </c>
       <c r="R16" t="n">
-        <v>7157681</v>
+        <v>7157667</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2366,38 +2366,38 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128964180</v>
+        <v>128963674</v>
       </c>
       <c r="B18" t="n">
-        <v>79124</v>
+        <v>91473</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -2408,10 +2408,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>776839</v>
+        <v>776962</v>
       </c>
       <c r="R18" t="n">
-        <v>7157679</v>
+        <v>7157631</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2471,41 +2471,42 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128963674</v>
+        <v>128963540</v>
       </c>
       <c r="B19" t="n">
-        <v>91473</v>
+        <v>98636</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2513,10 +2514,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>776962</v>
+        <v>777003</v>
       </c>
       <c r="R19" t="n">
-        <v>7157631</v>
+        <v>7157598</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2576,42 +2577,41 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128963540</v>
+        <v>128964180</v>
       </c>
       <c r="B20" t="n">
-        <v>98636</v>
+        <v>79124</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2619,10 +2619,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>777003</v>
+        <v>776839</v>
       </c>
       <c r="R20" t="n">
-        <v>7157598</v>
+        <v>7157679</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3007,32 +3007,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128963189</v>
+        <v>128963073</v>
       </c>
       <c r="B24" t="n">
-        <v>91473</v>
+        <v>82983</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3049,10 +3049,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>776995</v>
+        <v>776971</v>
       </c>
       <c r="R24" t="n">
-        <v>7157615</v>
+        <v>7157600</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3112,32 +3112,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128963073</v>
+        <v>128963189</v>
       </c>
       <c r="B25" t="n">
-        <v>82983</v>
+        <v>91473</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3154,10 +3154,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>776971</v>
+        <v>776995</v>
       </c>
       <c r="R25" t="n">
-        <v>7157600</v>
+        <v>7157615</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3433,10 +3433,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128963646</v>
+        <v>128963722</v>
       </c>
       <c r="B28" t="n">
-        <v>82983</v>
+        <v>91458</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3444,21 +3444,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1312</v>
+        <v>112</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3475,10 +3475,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>777005</v>
+        <v>776951</v>
       </c>
       <c r="R28" t="n">
-        <v>7157660</v>
+        <v>7157658</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3538,10 +3538,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128963722</v>
+        <v>128963646</v>
       </c>
       <c r="B29" t="n">
-        <v>91458</v>
+        <v>82983</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3549,21 +3549,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>112</v>
+        <v>1312</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3580,10 +3580,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>776951</v>
+        <v>777005</v>
       </c>
       <c r="R29" t="n">
-        <v>7157658</v>
+        <v>7157660</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3643,32 +3643,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128963560</v>
+        <v>128963102</v>
       </c>
       <c r="B30" t="n">
-        <v>91473</v>
+        <v>91508</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3685,10 +3685,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>777002</v>
+        <v>776998</v>
       </c>
       <c r="R30" t="n">
-        <v>7157629</v>
+        <v>7157616</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3748,7 +3748,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128963102</v>
+        <v>128964019</v>
       </c>
       <c r="B31" t="n">
         <v>91508</v>
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>776998</v>
+        <v>776903</v>
       </c>
       <c r="R31" t="n">
-        <v>7157616</v>
+        <v>7157641</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3853,32 +3853,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128964019</v>
+        <v>128963560</v>
       </c>
       <c r="B32" t="n">
-        <v>91508</v>
+        <v>91473</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3895,10 +3895,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>776903</v>
+        <v>777002</v>
       </c>
       <c r="R32" t="n">
-        <v>7157641</v>
+        <v>7157629</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>

--- a/artfynd/A 46103-2025 artfynd.xlsx
+++ b/artfynd/A 46103-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128964143</v>
+        <v>128964083</v>
       </c>
       <c r="B2" t="n">
-        <v>79124</v>
+        <v>91513</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,30 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -721,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>776873</v>
+        <v>776887</v>
       </c>
       <c r="R2" t="n">
-        <v>7157628</v>
+        <v>7157655</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,11 +753,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-02</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>fertil!</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,7 +783,7 @@
         <v>128963916</v>
       </c>
       <c r="B3" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,10 +885,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128964083</v>
+        <v>128964143</v>
       </c>
       <c r="B4" t="n">
-        <v>91508</v>
+        <v>79029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,30 +896,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -936,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>776887</v>
+        <v>776873</v>
       </c>
       <c r="R4" t="n">
-        <v>7157655</v>
+        <v>7157628</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,6 +967,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>fertil!</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1002,7 +1002,7 @@
         <v>128963639</v>
       </c>
       <c r="B5" t="n">
-        <v>82983</v>
+        <v>82892</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1104,32 +1104,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128964110</v>
+        <v>128964270</v>
       </c>
       <c r="B6" t="n">
-        <v>91458</v>
+        <v>91967</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>112</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1146,10 +1146,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>776877</v>
+        <v>776865</v>
       </c>
       <c r="R6" t="n">
-        <v>7157631</v>
+        <v>7157670</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1209,10 +1209,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128963706</v>
+        <v>128964110</v>
       </c>
       <c r="B7" t="n">
-        <v>91458</v>
+        <v>91463</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,10 +1251,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>776952</v>
+        <v>776877</v>
       </c>
       <c r="R7" t="n">
-        <v>7157667</v>
+        <v>7157631</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,32 +1314,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128964270</v>
+        <v>128963706</v>
       </c>
       <c r="B8" t="n">
-        <v>91962</v>
+        <v>91463</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>112</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1356,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>776865</v>
+        <v>776952</v>
       </c>
       <c r="R8" t="n">
-        <v>7157670</v>
+        <v>7157667</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,7 +1422,7 @@
         <v>128963556</v>
       </c>
       <c r="B9" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>128963515</v>
       </c>
       <c r="B10" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>128964297</v>
       </c>
       <c r="B11" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1735,32 +1735,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128963423</v>
+        <v>128963275</v>
       </c>
       <c r="B12" t="n">
-        <v>91473</v>
+        <v>91513</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>777013</v>
+        <v>776991</v>
       </c>
       <c r="R12" t="n">
-        <v>7157604</v>
+        <v>7157610</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1840,32 +1840,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128963275</v>
+        <v>128963423</v>
       </c>
       <c r="B13" t="n">
-        <v>91508</v>
+        <v>91478</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1882,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>776991</v>
+        <v>777013</v>
       </c>
       <c r="R13" t="n">
-        <v>7157610</v>
+        <v>7157604</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1945,10 +1945,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128964198</v>
+        <v>128963824</v>
       </c>
       <c r="B14" t="n">
-        <v>91508</v>
+        <v>79029</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1956,29 +1956,25 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
@@ -1987,10 +1983,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>776862</v>
+        <v>776924</v>
       </c>
       <c r="R14" t="n">
-        <v>7157681</v>
+        <v>7157645</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2050,10 +2046,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128963824</v>
+        <v>128964345</v>
       </c>
       <c r="B15" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2079,7 +2075,11 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
@@ -2088,10 +2088,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>776924</v>
+        <v>776870</v>
       </c>
       <c r="R15" t="n">
-        <v>7157645</v>
+        <v>7157667</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2151,10 +2151,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128964345</v>
+        <v>128964198</v>
       </c>
       <c r="B16" t="n">
-        <v>79124</v>
+        <v>91513</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2162,27 +2162,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -2193,10 +2193,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>776870</v>
+        <v>776862</v>
       </c>
       <c r="R16" t="n">
-        <v>7157667</v>
+        <v>7157681</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2256,42 +2256,42 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128964055</v>
+        <v>128963540</v>
       </c>
       <c r="B17" t="n">
-        <v>57717</v>
+        <v>98643</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2299,10 +2299,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>776909</v>
+        <v>777003</v>
       </c>
       <c r="R17" t="n">
-        <v>7157645</v>
+        <v>7157598</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2337,17 +2337,13 @@
           <t>2025-10-02</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>hack i låga</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2369,7 +2365,7 @@
         <v>128963674</v>
       </c>
       <c r="B18" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2471,42 +2467,42 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128963540</v>
+        <v>128964055</v>
       </c>
       <c r="B19" t="n">
-        <v>98636</v>
+        <v>57720</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2514,10 +2510,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>777003</v>
+        <v>776909</v>
       </c>
       <c r="R19" t="n">
-        <v>7157598</v>
+        <v>7157645</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2552,13 +2548,17 @@
           <t>2025-10-02</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>hack i låga</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2580,7 +2580,7 @@
         <v>128964180</v>
       </c>
       <c r="B20" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2685,7 +2685,7 @@
         <v>128964009</v>
       </c>
       <c r="B21" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2790,7 +2790,7 @@
         <v>128964410</v>
       </c>
       <c r="B22" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>128963395</v>
       </c>
       <c r="B23" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3010,7 +3010,7 @@
         <v>128963073</v>
       </c>
       <c r="B24" t="n">
-        <v>82983</v>
+        <v>82892</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         <v>128963189</v>
       </c>
       <c r="B25" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>128964193</v>
       </c>
       <c r="B26" t="n">
-        <v>91962</v>
+        <v>91967</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>128963472</v>
       </c>
       <c r="B27" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
         <v>128963722</v>
       </c>
       <c r="B28" t="n">
-        <v>91458</v>
+        <v>91463</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3541,7 +3541,7 @@
         <v>128963646</v>
       </c>
       <c r="B29" t="n">
-        <v>82983</v>
+        <v>82892</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>128963102</v>
       </c>
       <c r="B30" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>128964019</v>
       </c>
       <c r="B31" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>128963560</v>
       </c>
       <c r="B32" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3961,7 +3961,7 @@
         <v>128963966</v>
       </c>
       <c r="B33" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>128974663</v>
       </c>
       <c r="B34" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>128974745</v>
       </c>
       <c r="B35" t="n">
-        <v>91526</v>
+        <v>91531</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4281,7 +4281,7 @@
         <v>128973835</v>
       </c>
       <c r="B36" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 46103-2025 artfynd.xlsx
+++ b/artfynd/A 46103-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128964083</v>
+        <v>128964143</v>
       </c>
       <c r="B2" t="n">
-        <v>91520</v>
+        <v>79034</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,30 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -717,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>776887</v>
+        <v>776873</v>
       </c>
       <c r="R2" t="n">
-        <v>7157655</v>
+        <v>7157628</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,6 +757,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>fertil!</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,32 +789,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128963916</v>
+        <v>128964083</v>
       </c>
       <c r="B3" t="n">
-        <v>91485</v>
+        <v>91520</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>776921</v>
+        <v>776887</v>
       </c>
       <c r="R3" t="n">
-        <v>7157641</v>
+        <v>7157655</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,45 +894,41 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128964143</v>
+        <v>128963916</v>
       </c>
       <c r="B4" t="n">
-        <v>79034</v>
+        <v>91485</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -931,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>776873</v>
+        <v>776921</v>
       </c>
       <c r="R4" t="n">
-        <v>7157628</v>
+        <v>7157641</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -967,11 +972,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-02</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>fertil!</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -3217,10 +3217,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128964193</v>
+        <v>128963472</v>
       </c>
       <c r="B26" t="n">
-        <v>91975</v>
+        <v>98651</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3228,30 +3228,31 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3259,10 +3260,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>776862</v>
+        <v>777013</v>
       </c>
       <c r="R26" t="n">
-        <v>7157681</v>
+        <v>7157601</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3295,6 +3296,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>ca 2 x 2 meter med bladrosetter!</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3322,10 +3328,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128963472</v>
+        <v>128964193</v>
       </c>
       <c r="B27" t="n">
-        <v>98651</v>
+        <v>91975</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3333,31 +3339,30 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3365,10 +3370,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>777013</v>
+        <v>776862</v>
       </c>
       <c r="R27" t="n">
-        <v>7157601</v>
+        <v>7157681</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3401,11 +3406,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-02</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>ca 2 x 2 meter med bladrosetter!</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3433,10 +3433,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128963722</v>
+        <v>128963646</v>
       </c>
       <c r="B28" t="n">
-        <v>91470</v>
+        <v>82897</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3444,21 +3444,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>112</v>
+        <v>1312</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3475,10 +3475,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>776951</v>
+        <v>777005</v>
       </c>
       <c r="R28" t="n">
-        <v>7157658</v>
+        <v>7157660</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3538,10 +3538,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128963646</v>
+        <v>128963722</v>
       </c>
       <c r="B29" t="n">
-        <v>82897</v>
+        <v>91470</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3549,21 +3549,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1312</v>
+        <v>112</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3580,10 +3580,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>777005</v>
+        <v>776951</v>
       </c>
       <c r="R29" t="n">
-        <v>7157660</v>
+        <v>7157658</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>

--- a/artfynd/A 46103-2025 artfynd.xlsx
+++ b/artfynd/A 46103-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128964143</v>
+        <v>128964083</v>
       </c>
       <c r="B2" t="n">
-        <v>79034</v>
+        <v>91523</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,30 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -721,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>776873</v>
+        <v>776887</v>
       </c>
       <c r="R2" t="n">
-        <v>7157628</v>
+        <v>7157655</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,11 +753,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-02</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>fertil!</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,32 +780,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128964083</v>
+        <v>128963916</v>
       </c>
       <c r="B3" t="n">
-        <v>91520</v>
+        <v>91488</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>776887</v>
+        <v>776921</v>
       </c>
       <c r="R3" t="n">
-        <v>7157655</v>
+        <v>7157641</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -894,41 +885,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128963916</v>
+        <v>128964143</v>
       </c>
       <c r="B4" t="n">
-        <v>91485</v>
+        <v>79034</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -936,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>776921</v>
+        <v>776873</v>
       </c>
       <c r="R4" t="n">
-        <v>7157641</v>
+        <v>7157628</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,6 +967,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>fertil!</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1107,7 +1107,7 @@
         <v>128964270</v>
       </c>
       <c r="B6" t="n">
-        <v>91975</v>
+        <v>91978</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>128964110</v>
       </c>
       <c r="B7" t="n">
-        <v>91470</v>
+        <v>91473</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>128963706</v>
       </c>
       <c r="B8" t="n">
-        <v>91470</v>
+        <v>91473</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1422,7 +1422,7 @@
         <v>128963556</v>
       </c>
       <c r="B9" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>128964297</v>
       </c>
       <c r="B10" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>128963515</v>
       </c>
       <c r="B11" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>128963275</v>
       </c>
       <c r="B12" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>128963423</v>
       </c>
       <c r="B13" t="n">
-        <v>91485</v>
+        <v>91488</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>128964198</v>
       </c>
       <c r="B14" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2256,42 +2256,41 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128963540</v>
+        <v>128964180</v>
       </c>
       <c r="B17" t="n">
-        <v>98651</v>
+        <v>79034</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2299,10 +2298,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>777003</v>
+        <v>776839</v>
       </c>
       <c r="R17" t="n">
-        <v>7157598</v>
+        <v>7157679</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2365,7 +2364,7 @@
         <v>128963674</v>
       </c>
       <c r="B18" t="n">
-        <v>91485</v>
+        <v>91488</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2577,41 +2576,42 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128964180</v>
+        <v>128963540</v>
       </c>
       <c r="B20" t="n">
-        <v>79034</v>
+        <v>98656</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2619,10 +2619,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>776839</v>
+        <v>777003</v>
       </c>
       <c r="R20" t="n">
-        <v>7157679</v>
+        <v>7157598</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2790,7 +2790,7 @@
         <v>128964410</v>
       </c>
       <c r="B22" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>128963395</v>
       </c>
       <c r="B23" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         <v>128963189</v>
       </c>
       <c r="B25" t="n">
-        <v>91485</v>
+        <v>91488</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3217,10 +3217,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128963472</v>
+        <v>128964193</v>
       </c>
       <c r="B26" t="n">
-        <v>98651</v>
+        <v>91978</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3228,31 +3228,30 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3260,10 +3259,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>777013</v>
+        <v>776862</v>
       </c>
       <c r="R26" t="n">
-        <v>7157601</v>
+        <v>7157681</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3296,11 +3295,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-02</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>ca 2 x 2 meter med bladrosetter!</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3328,10 +3322,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128964193</v>
+        <v>128963472</v>
       </c>
       <c r="B27" t="n">
-        <v>91975</v>
+        <v>98656</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3339,30 +3333,31 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3370,10 +3365,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>776862</v>
+        <v>777013</v>
       </c>
       <c r="R27" t="n">
-        <v>7157681</v>
+        <v>7157601</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3406,6 +3401,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>ca 2 x 2 meter med bladrosetter!</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3433,10 +3433,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128963646</v>
+        <v>128963722</v>
       </c>
       <c r="B28" t="n">
-        <v>82897</v>
+        <v>91473</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3444,21 +3444,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1312</v>
+        <v>112</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3475,10 +3475,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>777005</v>
+        <v>776951</v>
       </c>
       <c r="R28" t="n">
-        <v>7157660</v>
+        <v>7157658</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3538,10 +3538,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128963722</v>
+        <v>128963646</v>
       </c>
       <c r="B29" t="n">
-        <v>91470</v>
+        <v>82897</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3549,21 +3549,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>112</v>
+        <v>1312</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3580,10 +3580,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>776951</v>
+        <v>777005</v>
       </c>
       <c r="R29" t="n">
-        <v>7157658</v>
+        <v>7157660</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3646,7 +3646,7 @@
         <v>128963102</v>
       </c>
       <c r="B30" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>128964019</v>
       </c>
       <c r="B31" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>128963560</v>
       </c>
       <c r="B32" t="n">
-        <v>91485</v>
+        <v>91488</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>128974745</v>
       </c>
       <c r="B35" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 46103-2025 artfynd.xlsx
+++ b/artfynd/A 46103-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128964083</v>
       </c>
       <c r="B2" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>128963916</v>
       </c>
       <c r="B3" t="n">
-        <v>91488</v>
+        <v>91491</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>128964143</v>
       </c>
       <c r="B4" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>128963639</v>
       </c>
       <c r="B5" t="n">
-        <v>82897</v>
+        <v>82898</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>128964270</v>
       </c>
       <c r="B6" t="n">
-        <v>91978</v>
+        <v>91981</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>128964110</v>
       </c>
       <c r="B7" t="n">
-        <v>91473</v>
+        <v>91476</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>128963706</v>
       </c>
       <c r="B8" t="n">
-        <v>91473</v>
+        <v>91476</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1422,7 +1422,7 @@
         <v>128963556</v>
       </c>
       <c r="B9" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>128964297</v>
       </c>
       <c r="B10" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>128963515</v>
       </c>
       <c r="B11" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1735,32 +1735,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128963275</v>
+        <v>128963423</v>
       </c>
       <c r="B12" t="n">
-        <v>91523</v>
+        <v>91491</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>776991</v>
+        <v>777013</v>
       </c>
       <c r="R12" t="n">
-        <v>7157610</v>
+        <v>7157604</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1840,32 +1840,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128963423</v>
+        <v>128963275</v>
       </c>
       <c r="B13" t="n">
-        <v>91488</v>
+        <v>91526</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1882,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>777013</v>
+        <v>776991</v>
       </c>
       <c r="R13" t="n">
-        <v>7157604</v>
+        <v>7157610</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1948,7 +1948,7 @@
         <v>128964198</v>
       </c>
       <c r="B14" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>128963824</v>
       </c>
       <c r="B15" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>128964345</v>
       </c>
       <c r="B16" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2256,38 +2256,38 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128964180</v>
+        <v>128963674</v>
       </c>
       <c r="B17" t="n">
-        <v>79034</v>
+        <v>91491</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -2298,10 +2298,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>776839</v>
+        <v>776962</v>
       </c>
       <c r="R17" t="n">
-        <v>7157679</v>
+        <v>7157631</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2361,41 +2361,42 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128963674</v>
+        <v>128964055</v>
       </c>
       <c r="B18" t="n">
-        <v>91488</v>
+        <v>57720</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2403,10 +2404,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>776962</v>
+        <v>776909</v>
       </c>
       <c r="R18" t="n">
-        <v>7157631</v>
+        <v>7157645</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2441,13 +2442,17 @@
           <t>2025-10-02</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>hack i låga</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2466,10 +2471,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128964055</v>
+        <v>128964180</v>
       </c>
       <c r="B19" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2477,31 +2482,30 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2509,10 +2513,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>776909</v>
+        <v>776839</v>
       </c>
       <c r="R19" t="n">
-        <v>7157645</v>
+        <v>7157679</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2547,17 +2551,13 @@
           <t>2025-10-02</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>hack i låga</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2579,7 +2579,7 @@
         <v>128963540</v>
       </c>
       <c r="B20" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2685,7 +2685,7 @@
         <v>128964009</v>
       </c>
       <c r="B21" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2790,7 +2790,7 @@
         <v>128964410</v>
       </c>
       <c r="B22" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>128963395</v>
       </c>
       <c r="B23" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3010,7 +3010,7 @@
         <v>128963073</v>
       </c>
       <c r="B24" t="n">
-        <v>82897</v>
+        <v>82898</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         <v>128963189</v>
       </c>
       <c r="B25" t="n">
-        <v>91488</v>
+        <v>91491</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>128964193</v>
       </c>
       <c r="B26" t="n">
-        <v>91978</v>
+        <v>91981</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>128963472</v>
       </c>
       <c r="B27" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
         <v>128963722</v>
       </c>
       <c r="B28" t="n">
-        <v>91473</v>
+        <v>91476</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3541,7 +3541,7 @@
         <v>128963646</v>
       </c>
       <c r="B29" t="n">
-        <v>82897</v>
+        <v>82898</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>128963102</v>
       </c>
       <c r="B30" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>128964019</v>
       </c>
       <c r="B31" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>128963560</v>
       </c>
       <c r="B32" t="n">
-        <v>91488</v>
+        <v>91491</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>128974663</v>
       </c>
       <c r="B34" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>128974745</v>
       </c>
       <c r="B35" t="n">
-        <v>91541</v>
+        <v>91544</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4281,7 +4281,7 @@
         <v>128973835</v>
       </c>
       <c r="B36" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 46103-2025 artfynd.xlsx
+++ b/artfynd/A 46103-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128964083</v>
+        <v>128963916</v>
       </c>
       <c r="B2" t="n">
-        <v>91526</v>
+        <v>91491</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -717,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>776887</v>
+        <v>776921</v>
       </c>
       <c r="R2" t="n">
-        <v>7157655</v>
+        <v>7157641</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -780,41 +780,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128963916</v>
+        <v>128964143</v>
       </c>
       <c r="B3" t="n">
-        <v>91491</v>
+        <v>79035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -822,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>776921</v>
+        <v>776873</v>
       </c>
       <c r="R3" t="n">
-        <v>7157641</v>
+        <v>7157628</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,6 +862,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>fertil!</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128964143</v>
+        <v>128964083</v>
       </c>
       <c r="B4" t="n">
-        <v>79035</v>
+        <v>91526</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -896,34 +905,30 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -931,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>776873</v>
+        <v>776887</v>
       </c>
       <c r="R4" t="n">
-        <v>7157628</v>
+        <v>7157655</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -967,11 +972,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-02</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>fertil!</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1104,32 +1104,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128964270</v>
+        <v>128964110</v>
       </c>
       <c r="B6" t="n">
-        <v>91981</v>
+        <v>91476</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>112</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1146,10 +1146,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>776865</v>
+        <v>776877</v>
       </c>
       <c r="R6" t="n">
-        <v>7157670</v>
+        <v>7157631</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1209,7 +1209,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128964110</v>
+        <v>128963706</v>
       </c>
       <c r="B7" t="n">
         <v>91476</v>
@@ -1251,10 +1251,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>776877</v>
+        <v>776952</v>
       </c>
       <c r="R7" t="n">
-        <v>7157631</v>
+        <v>7157667</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,32 +1314,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128963706</v>
+        <v>128964270</v>
       </c>
       <c r="B8" t="n">
-        <v>91476</v>
+        <v>91981</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>112</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1356,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>776952</v>
+        <v>776865</v>
       </c>
       <c r="R8" t="n">
-        <v>7157667</v>
+        <v>7157670</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1524,41 +1524,42 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128964297</v>
+        <v>128963515</v>
       </c>
       <c r="B10" t="n">
-        <v>91526</v>
+        <v>98659</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1566,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>776865</v>
+        <v>777009</v>
       </c>
       <c r="R10" t="n">
-        <v>7157670</v>
+        <v>7157591</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,42 +1630,41 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128963515</v>
+        <v>128964297</v>
       </c>
       <c r="B11" t="n">
-        <v>98659</v>
+        <v>91526</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1672,10 +1672,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>777009</v>
+        <v>776865</v>
       </c>
       <c r="R11" t="n">
-        <v>7157591</v>
+        <v>7157670</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,32 +1735,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128963423</v>
+        <v>128963275</v>
       </c>
       <c r="B12" t="n">
-        <v>91491</v>
+        <v>91526</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>777013</v>
+        <v>776991</v>
       </c>
       <c r="R12" t="n">
-        <v>7157604</v>
+        <v>7157610</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1840,32 +1840,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128963275</v>
+        <v>128963423</v>
       </c>
       <c r="B13" t="n">
-        <v>91526</v>
+        <v>91491</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1882,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>776991</v>
+        <v>777013</v>
       </c>
       <c r="R13" t="n">
-        <v>7157610</v>
+        <v>7157604</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2256,38 +2256,38 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128963674</v>
+        <v>128964180</v>
       </c>
       <c r="B17" t="n">
-        <v>91491</v>
+        <v>79035</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -2298,10 +2298,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>776962</v>
+        <v>776839</v>
       </c>
       <c r="R17" t="n">
-        <v>7157631</v>
+        <v>7157679</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2361,42 +2361,41 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128964055</v>
+        <v>128963674</v>
       </c>
       <c r="B18" t="n">
-        <v>57720</v>
+        <v>91491</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2404,10 +2403,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>776909</v>
+        <v>776962</v>
       </c>
       <c r="R18" t="n">
-        <v>7157645</v>
+        <v>7157631</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2442,17 +2441,13 @@
           <t>2025-10-02</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>hack i låga</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2471,10 +2466,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128964180</v>
+        <v>128964055</v>
       </c>
       <c r="B19" t="n">
-        <v>79035</v>
+        <v>57720</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2482,30 +2477,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2513,10 +2509,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>776839</v>
+        <v>776909</v>
       </c>
       <c r="R19" t="n">
-        <v>7157679</v>
+        <v>7157645</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2551,13 +2547,17 @@
           <t>2025-10-02</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>hack i låga</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -3217,10 +3217,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128964193</v>
+        <v>128963472</v>
       </c>
       <c r="B26" t="n">
-        <v>91981</v>
+        <v>98659</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3228,30 +3228,31 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3259,10 +3260,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>776862</v>
+        <v>777013</v>
       </c>
       <c r="R26" t="n">
-        <v>7157681</v>
+        <v>7157601</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3295,6 +3296,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>ca 2 x 2 meter med bladrosetter!</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3322,10 +3328,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128963472</v>
+        <v>128964193</v>
       </c>
       <c r="B27" t="n">
-        <v>98659</v>
+        <v>91981</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3333,31 +3339,30 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3365,10 +3370,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>777013</v>
+        <v>776862</v>
       </c>
       <c r="R27" t="n">
-        <v>7157601</v>
+        <v>7157681</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3401,11 +3406,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-02</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>ca 2 x 2 meter med bladrosetter!</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 46103-2025 artfynd.xlsx
+++ b/artfynd/A 46103-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128963916</v>
+        <v>128964083</v>
       </c>
       <c r="B2" t="n">
-        <v>91491</v>
+        <v>91526</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -717,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>776921</v>
+        <v>776887</v>
       </c>
       <c r="R2" t="n">
-        <v>7157641</v>
+        <v>7157655</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -780,45 +780,41 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128964143</v>
+        <v>128963916</v>
       </c>
       <c r="B3" t="n">
-        <v>79035</v>
+        <v>91491</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -826,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>776873</v>
+        <v>776921</v>
       </c>
       <c r="R3" t="n">
-        <v>7157628</v>
+        <v>7157641</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-02</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>fertil!</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,10 +885,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128964083</v>
+        <v>128964143</v>
       </c>
       <c r="B4" t="n">
-        <v>91526</v>
+        <v>79035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,30 +896,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -936,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>776887</v>
+        <v>776873</v>
       </c>
       <c r="R4" t="n">
-        <v>7157655</v>
+        <v>7157628</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,6 +967,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>fertil!</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -3217,10 +3217,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128963472</v>
+        <v>128964193</v>
       </c>
       <c r="B26" t="n">
-        <v>98659</v>
+        <v>91981</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3228,31 +3228,30 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3260,10 +3259,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>777013</v>
+        <v>776862</v>
       </c>
       <c r="R26" t="n">
-        <v>7157601</v>
+        <v>7157681</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3296,11 +3295,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-02</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>ca 2 x 2 meter med bladrosetter!</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3328,10 +3322,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128964193</v>
+        <v>128963472</v>
       </c>
       <c r="B27" t="n">
-        <v>91981</v>
+        <v>98659</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3339,30 +3333,31 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3370,10 +3365,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>776862</v>
+        <v>777013</v>
       </c>
       <c r="R27" t="n">
-        <v>7157681</v>
+        <v>7157601</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3406,6 +3401,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>ca 2 x 2 meter med bladrosetter!</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 46103-2025 artfynd.xlsx
+++ b/artfynd/A 46103-2025 artfynd.xlsx
@@ -1104,7 +1104,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128964110</v>
+        <v>128963706</v>
       </c>
       <c r="B6" t="n">
         <v>91476</v>
@@ -1146,10 +1146,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>776877</v>
+        <v>776952</v>
       </c>
       <c r="R6" t="n">
-        <v>7157631</v>
+        <v>7157667</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1209,7 +1209,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128963706</v>
+        <v>128964110</v>
       </c>
       <c r="B7" t="n">
         <v>91476</v>
@@ -1251,10 +1251,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>776952</v>
+        <v>776877</v>
       </c>
       <c r="R7" t="n">
-        <v>7157667</v>
+        <v>7157631</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1524,42 +1524,41 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128963515</v>
+        <v>128964297</v>
       </c>
       <c r="B10" t="n">
-        <v>98659</v>
+        <v>91526</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1567,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>777009</v>
+        <v>776865</v>
       </c>
       <c r="R10" t="n">
-        <v>7157591</v>
+        <v>7157670</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1630,41 +1629,42 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128964297</v>
+        <v>128963515</v>
       </c>
       <c r="B11" t="n">
-        <v>91526</v>
+        <v>98659</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1672,10 +1672,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>776865</v>
+        <v>777009</v>
       </c>
       <c r="R11" t="n">
-        <v>7157670</v>
+        <v>7157591</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1945,10 +1945,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128964198</v>
+        <v>128963824</v>
       </c>
       <c r="B14" t="n">
-        <v>91526</v>
+        <v>79035</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1956,29 +1956,25 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
@@ -1987,10 +1983,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>776862</v>
+        <v>776924</v>
       </c>
       <c r="R14" t="n">
-        <v>7157681</v>
+        <v>7157645</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2050,10 +2046,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128963824</v>
+        <v>128964198</v>
       </c>
       <c r="B15" t="n">
-        <v>79035</v>
+        <v>91526</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2061,25 +2057,29 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
@@ -2088,10 +2088,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>776924</v>
+        <v>776862</v>
       </c>
       <c r="R15" t="n">
-        <v>7157645</v>
+        <v>7157681</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2256,38 +2256,38 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128964180</v>
+        <v>128963674</v>
       </c>
       <c r="B17" t="n">
-        <v>79035</v>
+        <v>91491</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -2298,10 +2298,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>776839</v>
+        <v>776962</v>
       </c>
       <c r="R17" t="n">
-        <v>7157679</v>
+        <v>7157631</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2361,38 +2361,38 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128963674</v>
+        <v>128964180</v>
       </c>
       <c r="B18" t="n">
-        <v>91491</v>
+        <v>79035</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>776962</v>
+        <v>776839</v>
       </c>
       <c r="R18" t="n">
-        <v>7157631</v>
+        <v>7157679</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -3007,32 +3007,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128963073</v>
+        <v>128963189</v>
       </c>
       <c r="B24" t="n">
-        <v>82898</v>
+        <v>91491</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3049,10 +3049,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>776971</v>
+        <v>776995</v>
       </c>
       <c r="R24" t="n">
-        <v>7157600</v>
+        <v>7157615</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3112,32 +3112,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128963189</v>
+        <v>128963073</v>
       </c>
       <c r="B25" t="n">
-        <v>91491</v>
+        <v>82898</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3154,10 +3154,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>776995</v>
+        <v>776971</v>
       </c>
       <c r="R25" t="n">
-        <v>7157615</v>
+        <v>7157600</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3433,10 +3433,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128963722</v>
+        <v>128963646</v>
       </c>
       <c r="B28" t="n">
-        <v>91476</v>
+        <v>82898</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3444,21 +3444,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>112</v>
+        <v>1312</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3475,10 +3475,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>776951</v>
+        <v>777005</v>
       </c>
       <c r="R28" t="n">
-        <v>7157658</v>
+        <v>7157660</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3538,10 +3538,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128963646</v>
+        <v>128963722</v>
       </c>
       <c r="B29" t="n">
-        <v>82898</v>
+        <v>91476</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3549,21 +3549,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1312</v>
+        <v>112</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3580,10 +3580,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>777005</v>
+        <v>776951</v>
       </c>
       <c r="R29" t="n">
-        <v>7157660</v>
+        <v>7157658</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>

--- a/artfynd/A 46103-2025 artfynd.xlsx
+++ b/artfynd/A 46103-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128964083</v>
+        <v>128964143</v>
       </c>
       <c r="B2" t="n">
-        <v>91526</v>
+        <v>79039</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,30 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -717,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>776887</v>
+        <v>776873</v>
       </c>
       <c r="R2" t="n">
-        <v>7157655</v>
+        <v>7157628</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,6 +757,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>fertil!</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,32 +789,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128963916</v>
+        <v>128964083</v>
       </c>
       <c r="B3" t="n">
-        <v>91491</v>
+        <v>91533</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>776921</v>
+        <v>776887</v>
       </c>
       <c r="R3" t="n">
-        <v>7157641</v>
+        <v>7157655</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,45 +894,41 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128964143</v>
+        <v>128963916</v>
       </c>
       <c r="B4" t="n">
-        <v>79035</v>
+        <v>91497</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -931,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>776873</v>
+        <v>776921</v>
       </c>
       <c r="R4" t="n">
-        <v>7157628</v>
+        <v>7157641</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -967,11 +972,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-02</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>fertil!</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1002,7 +1002,7 @@
         <v>128963639</v>
       </c>
       <c r="B5" t="n">
-        <v>82898</v>
+        <v>82902</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1104,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128963706</v>
+        <v>128964110</v>
       </c>
       <c r="B6" t="n">
-        <v>91476</v>
+        <v>91482</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1146,10 +1146,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>776952</v>
+        <v>776877</v>
       </c>
       <c r="R6" t="n">
-        <v>7157667</v>
+        <v>7157631</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1209,10 +1209,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128964110</v>
+        <v>128963706</v>
       </c>
       <c r="B7" t="n">
-        <v>91476</v>
+        <v>91482</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,10 +1251,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>776877</v>
+        <v>776952</v>
       </c>
       <c r="R7" t="n">
-        <v>7157631</v>
+        <v>7157667</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,7 +1317,7 @@
         <v>128964270</v>
       </c>
       <c r="B8" t="n">
-        <v>91981</v>
+        <v>91988</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1422,7 +1422,7 @@
         <v>128963556</v>
       </c>
       <c r="B9" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>128964297</v>
       </c>
       <c r="B10" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>128963515</v>
       </c>
       <c r="B11" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>128963275</v>
       </c>
       <c r="B12" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>128963423</v>
       </c>
       <c r="B13" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>128963824</v>
       </c>
       <c r="B14" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2046,10 +2046,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128964198</v>
+        <v>128964345</v>
       </c>
       <c r="B15" t="n">
-        <v>91526</v>
+        <v>79039</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2057,27 +2057,27 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -2088,10 +2088,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>776862</v>
+        <v>776870</v>
       </c>
       <c r="R15" t="n">
-        <v>7157681</v>
+        <v>7157667</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2151,10 +2151,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128964345</v>
+        <v>128964198</v>
       </c>
       <c r="B16" t="n">
-        <v>79035</v>
+        <v>91533</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2162,27 +2162,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -2193,10 +2193,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>776870</v>
+        <v>776862</v>
       </c>
       <c r="R16" t="n">
-        <v>7157667</v>
+        <v>7157681</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2256,41 +2256,42 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128963674</v>
+        <v>128964055</v>
       </c>
       <c r="B17" t="n">
-        <v>91491</v>
+        <v>57722</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2298,10 +2299,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>776962</v>
+        <v>776909</v>
       </c>
       <c r="R17" t="n">
-        <v>7157631</v>
+        <v>7157645</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2336,13 +2337,17 @@
           <t>2025-10-02</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>hack i låga</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2364,7 +2369,7 @@
         <v>128964180</v>
       </c>
       <c r="B18" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2466,42 +2471,41 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128964055</v>
+        <v>128963674</v>
       </c>
       <c r="B19" t="n">
-        <v>57720</v>
+        <v>91497</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2509,10 +2513,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>776909</v>
+        <v>776962</v>
       </c>
       <c r="R19" t="n">
-        <v>7157645</v>
+        <v>7157631</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2547,17 +2551,13 @@
           <t>2025-10-02</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>hack i låga</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2579,7 +2579,7 @@
         <v>128963540</v>
       </c>
       <c r="B20" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2685,7 +2685,7 @@
         <v>128964009</v>
       </c>
       <c r="B21" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2790,7 +2790,7 @@
         <v>128964410</v>
       </c>
       <c r="B22" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>128963395</v>
       </c>
       <c r="B23" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3007,32 +3007,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128963189</v>
+        <v>128963073</v>
       </c>
       <c r="B24" t="n">
-        <v>91491</v>
+        <v>82902</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3049,10 +3049,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>776995</v>
+        <v>776971</v>
       </c>
       <c r="R24" t="n">
-        <v>7157615</v>
+        <v>7157600</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3112,32 +3112,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128963073</v>
+        <v>128963189</v>
       </c>
       <c r="B25" t="n">
-        <v>82898</v>
+        <v>91497</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3154,10 +3154,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>776971</v>
+        <v>776995</v>
       </c>
       <c r="R25" t="n">
-        <v>7157600</v>
+        <v>7157615</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3220,7 +3220,7 @@
         <v>128964193</v>
       </c>
       <c r="B26" t="n">
-        <v>91981</v>
+        <v>91988</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>128963472</v>
       </c>
       <c r="B27" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3433,10 +3433,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128963646</v>
+        <v>128963722</v>
       </c>
       <c r="B28" t="n">
-        <v>82898</v>
+        <v>91482</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3444,21 +3444,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1312</v>
+        <v>112</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3475,10 +3475,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>777005</v>
+        <v>776951</v>
       </c>
       <c r="R28" t="n">
-        <v>7157660</v>
+        <v>7157658</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3538,10 +3538,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128963722</v>
+        <v>128963646</v>
       </c>
       <c r="B29" t="n">
-        <v>91476</v>
+        <v>82902</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3549,21 +3549,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>112</v>
+        <v>1312</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3580,10 +3580,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>776951</v>
+        <v>777005</v>
       </c>
       <c r="R29" t="n">
-        <v>7157658</v>
+        <v>7157660</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3646,7 +3646,7 @@
         <v>128963102</v>
       </c>
       <c r="B30" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>128964019</v>
       </c>
       <c r="B31" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>128963560</v>
       </c>
       <c r="B32" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3961,7 +3961,7 @@
         <v>128963966</v>
       </c>
       <c r="B33" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>128974663</v>
       </c>
       <c r="B34" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>128974745</v>
       </c>
       <c r="B35" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4281,7 +4281,7 @@
         <v>128973835</v>
       </c>
       <c r="B36" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 46103-2025 artfynd.xlsx
+++ b/artfynd/A 46103-2025 artfynd.xlsx
@@ -1735,32 +1735,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128963275</v>
+        <v>128963423</v>
       </c>
       <c r="B12" t="n">
-        <v>91533</v>
+        <v>91497</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>776991</v>
+        <v>777013</v>
       </c>
       <c r="R12" t="n">
-        <v>7157610</v>
+        <v>7157604</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1840,32 +1840,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128963423</v>
+        <v>128963275</v>
       </c>
       <c r="B13" t="n">
-        <v>91497</v>
+        <v>91533</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1882,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>777013</v>
+        <v>776991</v>
       </c>
       <c r="R13" t="n">
-        <v>7157604</v>
+        <v>7157610</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 46103-2025 artfynd.xlsx
+++ b/artfynd/A 46103-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128964143</v>
+        <v>128964083</v>
       </c>
       <c r="B2" t="n">
-        <v>79039</v>
+        <v>91540</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,30 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -721,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>776873</v>
+        <v>776887</v>
       </c>
       <c r="R2" t="n">
-        <v>7157628</v>
+        <v>7157655</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,11 +753,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-02</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>fertil!</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,32 +780,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128964083</v>
+        <v>128963916</v>
       </c>
       <c r="B3" t="n">
-        <v>91533</v>
+        <v>91504</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>776887</v>
+        <v>776921</v>
       </c>
       <c r="R3" t="n">
-        <v>7157655</v>
+        <v>7157641</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -894,41 +885,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128963916</v>
+        <v>128964143</v>
       </c>
       <c r="B4" t="n">
-        <v>91497</v>
+        <v>79039</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -936,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>776921</v>
+        <v>776873</v>
       </c>
       <c r="R4" t="n">
-        <v>7157641</v>
+        <v>7157628</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,6 +967,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>fertil!</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1002,7 +1002,7 @@
         <v>128963639</v>
       </c>
       <c r="B5" t="n">
-        <v>82902</v>
+        <v>82871</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>128964110</v>
       </c>
       <c r="B6" t="n">
-        <v>91482</v>
+        <v>91489</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>128963706</v>
       </c>
       <c r="B7" t="n">
-        <v>91482</v>
+        <v>91489</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>128964270</v>
       </c>
       <c r="B8" t="n">
-        <v>91988</v>
+        <v>91995</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1422,7 +1422,7 @@
         <v>128963556</v>
       </c>
       <c r="B9" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>128964297</v>
       </c>
       <c r="B10" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>128963515</v>
       </c>
       <c r="B11" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>128963423</v>
       </c>
       <c r="B12" t="n">
-        <v>91497</v>
+        <v>91504</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>128963275</v>
       </c>
       <c r="B13" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1945,10 +1945,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128963824</v>
+        <v>128964198</v>
       </c>
       <c r="B14" t="n">
-        <v>79039</v>
+        <v>91540</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1956,25 +1956,29 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
@@ -1983,10 +1987,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>776924</v>
+        <v>776862</v>
       </c>
       <c r="R14" t="n">
-        <v>7157645</v>
+        <v>7157681</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2046,7 +2050,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128964345</v>
+        <v>128963824</v>
       </c>
       <c r="B15" t="n">
         <v>79039</v>
@@ -2075,11 +2079,7 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
@@ -2088,10 +2088,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>776870</v>
+        <v>776924</v>
       </c>
       <c r="R15" t="n">
-        <v>7157667</v>
+        <v>7157645</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2151,10 +2151,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128964198</v>
+        <v>128964345</v>
       </c>
       <c r="B16" t="n">
-        <v>91533</v>
+        <v>79039</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2162,27 +2162,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -2193,10 +2193,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>776862</v>
+        <v>776870</v>
       </c>
       <c r="R16" t="n">
-        <v>7157681</v>
+        <v>7157667</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2256,42 +2256,41 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128964055</v>
+        <v>128963674</v>
       </c>
       <c r="B17" t="n">
-        <v>57722</v>
+        <v>91504</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2299,10 +2298,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>776909</v>
+        <v>776962</v>
       </c>
       <c r="R17" t="n">
-        <v>7157645</v>
+        <v>7157631</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2337,17 +2336,13 @@
           <t>2025-10-02</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>hack i låga</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2366,41 +2361,42 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128964180</v>
+        <v>128963540</v>
       </c>
       <c r="B18" t="n">
-        <v>79039</v>
+        <v>98676</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2408,10 +2404,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>776839</v>
+        <v>777003</v>
       </c>
       <c r="R18" t="n">
-        <v>7157679</v>
+        <v>7157598</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2471,41 +2467,42 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128963674</v>
+        <v>128964055</v>
       </c>
       <c r="B19" t="n">
-        <v>91497</v>
+        <v>57722</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2513,10 +2510,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>776962</v>
+        <v>776909</v>
       </c>
       <c r="R19" t="n">
-        <v>7157631</v>
+        <v>7157645</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2551,13 +2548,17 @@
           <t>2025-10-02</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>hack i låga</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2576,42 +2577,41 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128963540</v>
+        <v>128964180</v>
       </c>
       <c r="B20" t="n">
-        <v>98669</v>
+        <v>79039</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2619,10 +2619,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>777003</v>
+        <v>776839</v>
       </c>
       <c r="R20" t="n">
-        <v>7157598</v>
+        <v>7157679</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2790,7 +2790,7 @@
         <v>128964410</v>
       </c>
       <c r="B22" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>128963395</v>
       </c>
       <c r="B23" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3010,7 +3010,7 @@
         <v>128963073</v>
       </c>
       <c r="B24" t="n">
-        <v>82902</v>
+        <v>82871</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         <v>128963189</v>
       </c>
       <c r="B25" t="n">
-        <v>91497</v>
+        <v>91504</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>128964193</v>
       </c>
       <c r="B26" t="n">
-        <v>91988</v>
+        <v>91995</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>128963472</v>
       </c>
       <c r="B27" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
         <v>128963722</v>
       </c>
       <c r="B28" t="n">
-        <v>91482</v>
+        <v>91489</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3541,7 +3541,7 @@
         <v>128963646</v>
       </c>
       <c r="B29" t="n">
-        <v>82902</v>
+        <v>82871</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>128963102</v>
       </c>
       <c r="B30" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>128964019</v>
       </c>
       <c r="B31" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>128963560</v>
       </c>
       <c r="B32" t="n">
-        <v>91497</v>
+        <v>91504</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>128974745</v>
       </c>
       <c r="B35" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 46103-2025 artfynd.xlsx
+++ b/artfynd/A 46103-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128964083</v>
+        <v>128964143</v>
       </c>
       <c r="B2" t="n">
-        <v>91540</v>
+        <v>79041</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,30 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -717,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>776887</v>
+        <v>776873</v>
       </c>
       <c r="R2" t="n">
-        <v>7157655</v>
+        <v>7157628</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,6 +757,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>fertil!</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,7 +792,7 @@
         <v>128963916</v>
       </c>
       <c r="B3" t="n">
-        <v>91504</v>
+        <v>91506</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128964143</v>
+        <v>128964083</v>
       </c>
       <c r="B4" t="n">
-        <v>79039</v>
+        <v>91542</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -896,34 +905,30 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -931,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>776873</v>
+        <v>776887</v>
       </c>
       <c r="R4" t="n">
-        <v>7157628</v>
+        <v>7157655</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -967,11 +972,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-02</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>fertil!</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1002,7 +1002,7 @@
         <v>128963639</v>
       </c>
       <c r="B5" t="n">
-        <v>82871</v>
+        <v>82873</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>128964110</v>
       </c>
       <c r="B6" t="n">
-        <v>91489</v>
+        <v>91491</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>128963706</v>
       </c>
       <c r="B7" t="n">
-        <v>91489</v>
+        <v>91491</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>128964270</v>
       </c>
       <c r="B8" t="n">
-        <v>91995</v>
+        <v>91997</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1422,7 +1422,7 @@
         <v>128963556</v>
       </c>
       <c r="B9" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1524,41 +1524,42 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128964297</v>
+        <v>128963515</v>
       </c>
       <c r="B10" t="n">
-        <v>91540</v>
+        <v>98678</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1566,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>776865</v>
+        <v>777009</v>
       </c>
       <c r="R10" t="n">
-        <v>7157670</v>
+        <v>7157591</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,42 +1630,41 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128963515</v>
+        <v>128964297</v>
       </c>
       <c r="B11" t="n">
-        <v>98676</v>
+        <v>91542</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1672,10 +1672,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>777009</v>
+        <v>776865</v>
       </c>
       <c r="R11" t="n">
-        <v>7157591</v>
+        <v>7157670</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1738,7 +1738,7 @@
         <v>128963423</v>
       </c>
       <c r="B12" t="n">
-        <v>91504</v>
+        <v>91506</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>128963275</v>
       </c>
       <c r="B13" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>128964198</v>
       </c>
       <c r="B14" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>128963824</v>
       </c>
       <c r="B15" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>128964345</v>
       </c>
       <c r="B16" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2256,38 +2256,38 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128963674</v>
+        <v>128964180</v>
       </c>
       <c r="B17" t="n">
-        <v>91504</v>
+        <v>79041</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -2298,10 +2298,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>776962</v>
+        <v>776839</v>
       </c>
       <c r="R17" t="n">
-        <v>7157631</v>
+        <v>7157679</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2361,42 +2361,41 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128963540</v>
+        <v>128963674</v>
       </c>
       <c r="B18" t="n">
-        <v>98676</v>
+        <v>91506</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2404,10 +2403,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>777003</v>
+        <v>776962</v>
       </c>
       <c r="R18" t="n">
-        <v>7157598</v>
+        <v>7157631</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2470,7 +2469,7 @@
         <v>128964055</v>
       </c>
       <c r="B19" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2577,41 +2576,42 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128964180</v>
+        <v>128963540</v>
       </c>
       <c r="B20" t="n">
-        <v>79039</v>
+        <v>98678</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2619,10 +2619,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>776839</v>
+        <v>777003</v>
       </c>
       <c r="R20" t="n">
-        <v>7157679</v>
+        <v>7157598</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2685,7 +2685,7 @@
         <v>128964009</v>
       </c>
       <c r="B21" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2790,7 +2790,7 @@
         <v>128964410</v>
       </c>
       <c r="B22" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>128963395</v>
       </c>
       <c r="B23" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3010,7 +3010,7 @@
         <v>128963073</v>
       </c>
       <c r="B24" t="n">
-        <v>82871</v>
+        <v>82873</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         <v>128963189</v>
       </c>
       <c r="B25" t="n">
-        <v>91504</v>
+        <v>91506</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>128964193</v>
       </c>
       <c r="B26" t="n">
-        <v>91995</v>
+        <v>91997</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>128963472</v>
       </c>
       <c r="B27" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
         <v>128963722</v>
       </c>
       <c r="B28" t="n">
-        <v>91489</v>
+        <v>91491</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3541,7 +3541,7 @@
         <v>128963646</v>
       </c>
       <c r="B29" t="n">
-        <v>82871</v>
+        <v>82873</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3643,32 +3643,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128963102</v>
+        <v>128963560</v>
       </c>
       <c r="B30" t="n">
-        <v>91540</v>
+        <v>91506</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3685,10 +3685,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>776998</v>
+        <v>777002</v>
       </c>
       <c r="R30" t="n">
-        <v>7157616</v>
+        <v>7157629</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3748,10 +3748,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128964019</v>
+        <v>128963102</v>
       </c>
       <c r="B31" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>776903</v>
+        <v>776998</v>
       </c>
       <c r="R31" t="n">
-        <v>7157641</v>
+        <v>7157616</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3853,32 +3853,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128963560</v>
+        <v>128964019</v>
       </c>
       <c r="B32" t="n">
-        <v>91504</v>
+        <v>91542</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3895,10 +3895,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>777002</v>
+        <v>776903</v>
       </c>
       <c r="R32" t="n">
-        <v>7157629</v>
+        <v>7157641</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3961,7 +3961,7 @@
         <v>128963966</v>
       </c>
       <c r="B33" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>128974663</v>
       </c>
       <c r="B34" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>128974745</v>
       </c>
       <c r="B35" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4281,7 +4281,7 @@
         <v>128973835</v>
       </c>
       <c r="B36" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 46103-2025 artfynd.xlsx
+++ b/artfynd/A 46103-2025 artfynd.xlsx
@@ -675,45 +675,41 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128964143</v>
+        <v>128963916</v>
       </c>
       <c r="B2" t="n">
-        <v>79041</v>
+        <v>91506</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -721,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>776873</v>
+        <v>776921</v>
       </c>
       <c r="R2" t="n">
-        <v>7157628</v>
+        <v>7157641</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,11 +753,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-02</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>fertil!</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,32 +780,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128963916</v>
+        <v>128964083</v>
       </c>
       <c r="B3" t="n">
-        <v>91506</v>
+        <v>91542</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>776921</v>
+        <v>776887</v>
       </c>
       <c r="R3" t="n">
-        <v>7157641</v>
+        <v>7157655</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -894,10 +885,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128964083</v>
+        <v>128964143</v>
       </c>
       <c r="B4" t="n">
-        <v>91542</v>
+        <v>79041</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,30 +896,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -936,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>776887</v>
+        <v>776873</v>
       </c>
       <c r="R4" t="n">
-        <v>7157655</v>
+        <v>7157628</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,6 +967,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>fertil!</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1524,42 +1524,41 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128963515</v>
+        <v>128964297</v>
       </c>
       <c r="B10" t="n">
-        <v>98678</v>
+        <v>91542</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1567,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>777009</v>
+        <v>776865</v>
       </c>
       <c r="R10" t="n">
-        <v>7157591</v>
+        <v>7157670</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1630,41 +1629,42 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128964297</v>
+        <v>128963515</v>
       </c>
       <c r="B11" t="n">
-        <v>91542</v>
+        <v>98678</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1672,10 +1672,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>776865</v>
+        <v>777009</v>
       </c>
       <c r="R11" t="n">
-        <v>7157670</v>
+        <v>7157591</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,32 +1735,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128963423</v>
+        <v>128963275</v>
       </c>
       <c r="B12" t="n">
-        <v>91506</v>
+        <v>91542</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>777013</v>
+        <v>776991</v>
       </c>
       <c r="R12" t="n">
-        <v>7157604</v>
+        <v>7157610</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1840,32 +1840,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128963275</v>
+        <v>128963423</v>
       </c>
       <c r="B13" t="n">
-        <v>91542</v>
+        <v>91506</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1882,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>776991</v>
+        <v>777013</v>
       </c>
       <c r="R13" t="n">
-        <v>7157610</v>
+        <v>7157604</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2361,41 +2361,42 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128963674</v>
+        <v>128964055</v>
       </c>
       <c r="B18" t="n">
-        <v>91506</v>
+        <v>57724</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2403,10 +2404,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>776962</v>
+        <v>776909</v>
       </c>
       <c r="R18" t="n">
-        <v>7157631</v>
+        <v>7157645</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2441,13 +2442,17 @@
           <t>2025-10-02</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>hack i låga</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2466,42 +2471,41 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128964055</v>
+        <v>128963674</v>
       </c>
       <c r="B19" t="n">
-        <v>57724</v>
+        <v>91506</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2509,10 +2513,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>776909</v>
+        <v>776962</v>
       </c>
       <c r="R19" t="n">
-        <v>7157645</v>
+        <v>7157631</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2547,17 +2551,13 @@
           <t>2025-10-02</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>hack i låga</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -3217,10 +3217,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128964193</v>
+        <v>128963472</v>
       </c>
       <c r="B26" t="n">
-        <v>91997</v>
+        <v>98678</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3228,30 +3228,31 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3259,10 +3260,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>776862</v>
+        <v>777013</v>
       </c>
       <c r="R26" t="n">
-        <v>7157681</v>
+        <v>7157601</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3295,6 +3296,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>ca 2 x 2 meter med bladrosetter!</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3322,10 +3328,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128963472</v>
+        <v>128964193</v>
       </c>
       <c r="B27" t="n">
-        <v>98678</v>
+        <v>91997</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3333,31 +3339,30 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3365,10 +3370,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>777013</v>
+        <v>776862</v>
       </c>
       <c r="R27" t="n">
-        <v>7157601</v>
+        <v>7157681</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3401,11 +3406,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-02</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>ca 2 x 2 meter med bladrosetter!</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3433,10 +3433,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128963722</v>
+        <v>128963646</v>
       </c>
       <c r="B28" t="n">
-        <v>91491</v>
+        <v>82873</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3444,21 +3444,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>112</v>
+        <v>1312</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3475,10 +3475,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>776951</v>
+        <v>777005</v>
       </c>
       <c r="R28" t="n">
-        <v>7157658</v>
+        <v>7157660</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3538,10 +3538,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128963646</v>
+        <v>128963722</v>
       </c>
       <c r="B29" t="n">
-        <v>82873</v>
+        <v>91491</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3549,21 +3549,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1312</v>
+        <v>112</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3580,10 +3580,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>777005</v>
+        <v>776951</v>
       </c>
       <c r="R29" t="n">
-        <v>7157660</v>
+        <v>7157658</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>

--- a/artfynd/A 46103-2025 artfynd.xlsx
+++ b/artfynd/A 46103-2025 artfynd.xlsx
@@ -3217,10 +3217,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128963472</v>
+        <v>128964193</v>
       </c>
       <c r="B26" t="n">
-        <v>98678</v>
+        <v>91997</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3228,31 +3228,30 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3260,10 +3259,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>777013</v>
+        <v>776862</v>
       </c>
       <c r="R26" t="n">
-        <v>7157601</v>
+        <v>7157681</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3296,11 +3295,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-02</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>ca 2 x 2 meter med bladrosetter!</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3328,10 +3322,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128964193</v>
+        <v>128963472</v>
       </c>
       <c r="B27" t="n">
-        <v>91997</v>
+        <v>98678</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3339,30 +3333,31 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3370,10 +3365,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>776862</v>
+        <v>777013</v>
       </c>
       <c r="R27" t="n">
-        <v>7157681</v>
+        <v>7157601</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3406,6 +3401,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>ca 2 x 2 meter med bladrosetter!</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 46103-2025 artfynd.xlsx
+++ b/artfynd/A 46103-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128963916</v>
+        <v>128964083</v>
       </c>
       <c r="B2" t="n">
-        <v>91506</v>
+        <v>91540</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -717,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>776921</v>
+        <v>776887</v>
       </c>
       <c r="R2" t="n">
-        <v>7157641</v>
+        <v>7157655</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -780,10 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128964083</v>
+        <v>128964143</v>
       </c>
       <c r="B3" t="n">
-        <v>91542</v>
+        <v>79041</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -791,30 +791,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -822,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>776887</v>
+        <v>776873</v>
       </c>
       <c r="R3" t="n">
-        <v>7157655</v>
+        <v>7157628</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,6 +862,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>fertil!</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,45 +894,41 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128964143</v>
+        <v>128963916</v>
       </c>
       <c r="B4" t="n">
-        <v>79041</v>
+        <v>91504</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -931,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>776873</v>
+        <v>776921</v>
       </c>
       <c r="R4" t="n">
-        <v>7157628</v>
+        <v>7157641</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -967,11 +972,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-02</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>fertil!</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1104,32 +1104,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128964110</v>
+        <v>128964270</v>
       </c>
       <c r="B6" t="n">
-        <v>91491</v>
+        <v>91992</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>112</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1146,10 +1146,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>776877</v>
+        <v>776865</v>
       </c>
       <c r="R6" t="n">
-        <v>7157631</v>
+        <v>7157670</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1209,7 +1209,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128963706</v>
+        <v>128964110</v>
       </c>
       <c r="B7" t="n">
         <v>91491</v>
@@ -1251,10 +1251,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>776952</v>
+        <v>776877</v>
       </c>
       <c r="R7" t="n">
-        <v>7157667</v>
+        <v>7157631</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,32 +1314,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128964270</v>
+        <v>128963706</v>
       </c>
       <c r="B8" t="n">
-        <v>91997</v>
+        <v>91491</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>112</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1356,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>776865</v>
+        <v>776952</v>
       </c>
       <c r="R8" t="n">
-        <v>7157670</v>
+        <v>7157667</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,7 +1422,7 @@
         <v>128963556</v>
       </c>
       <c r="B9" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>128964297</v>
       </c>
       <c r="B10" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>128963515</v>
       </c>
       <c r="B11" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1735,32 +1735,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128963275</v>
+        <v>128963423</v>
       </c>
       <c r="B12" t="n">
-        <v>91542</v>
+        <v>91504</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>776991</v>
+        <v>777013</v>
       </c>
       <c r="R12" t="n">
-        <v>7157610</v>
+        <v>7157604</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1840,32 +1840,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128963423</v>
+        <v>128963275</v>
       </c>
       <c r="B13" t="n">
-        <v>91506</v>
+        <v>91540</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1882,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>777013</v>
+        <v>776991</v>
       </c>
       <c r="R13" t="n">
-        <v>7157604</v>
+        <v>7157610</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1948,7 +1948,7 @@
         <v>128964198</v>
       </c>
       <c r="B14" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2361,42 +2361,41 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128964055</v>
+        <v>128963674</v>
       </c>
       <c r="B18" t="n">
-        <v>57724</v>
+        <v>91504</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2404,10 +2403,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>776909</v>
+        <v>776962</v>
       </c>
       <c r="R18" t="n">
-        <v>7157645</v>
+        <v>7157631</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2442,17 +2441,13 @@
           <t>2025-10-02</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>hack i låga</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2471,41 +2466,42 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128963674</v>
+        <v>128963540</v>
       </c>
       <c r="B19" t="n">
-        <v>91506</v>
+        <v>98704</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2513,10 +2509,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>776962</v>
+        <v>777003</v>
       </c>
       <c r="R19" t="n">
-        <v>7157631</v>
+        <v>7157598</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2576,42 +2572,42 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128963540</v>
+        <v>128964055</v>
       </c>
       <c r="B20" t="n">
-        <v>98678</v>
+        <v>57724</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2619,10 +2615,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>777003</v>
+        <v>776909</v>
       </c>
       <c r="R20" t="n">
-        <v>7157598</v>
+        <v>7157645</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2657,13 +2653,17 @@
           <t>2025-10-02</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>hack i låga</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2790,7 +2790,7 @@
         <v>128964410</v>
       </c>
       <c r="B22" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>128963395</v>
       </c>
       <c r="B23" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         <v>128963189</v>
       </c>
       <c r="B25" t="n">
-        <v>91506</v>
+        <v>91504</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>128964193</v>
       </c>
       <c r="B26" t="n">
-        <v>91997</v>
+        <v>91992</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3325,7 +3325,7 @@
         <v>128963472</v>
       </c>
       <c r="B27" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3643,32 +3643,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128963560</v>
+        <v>128963102</v>
       </c>
       <c r="B30" t="n">
-        <v>91506</v>
+        <v>91540</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3685,10 +3685,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>777002</v>
+        <v>776998</v>
       </c>
       <c r="R30" t="n">
-        <v>7157629</v>
+        <v>7157616</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3748,10 +3748,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128963102</v>
+        <v>128964019</v>
       </c>
       <c r="B31" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>776998</v>
+        <v>776903</v>
       </c>
       <c r="R31" t="n">
-        <v>7157616</v>
+        <v>7157641</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3853,32 +3853,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128964019</v>
+        <v>128963560</v>
       </c>
       <c r="B32" t="n">
-        <v>91542</v>
+        <v>91504</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3895,10 +3895,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>776903</v>
+        <v>777002</v>
       </c>
       <c r="R32" t="n">
-        <v>7157641</v>
+        <v>7157629</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4176,7 +4176,7 @@
         <v>128974745</v>
       </c>
       <c r="B35" t="n">
-        <v>91560</v>
+        <v>91558</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 46103-2025 artfynd.xlsx
+++ b/artfynd/A 46103-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128964083</v>
+        <v>128964143</v>
       </c>
       <c r="B2" t="n">
-        <v>91540</v>
+        <v>79041</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,30 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -717,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>776887</v>
+        <v>776873</v>
       </c>
       <c r="R2" t="n">
-        <v>7157655</v>
+        <v>7157628</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,6 +757,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>fertil!</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,45 +789,41 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128964143</v>
+        <v>128963916</v>
       </c>
       <c r="B3" t="n">
-        <v>79041</v>
+        <v>91504</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -826,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>776873</v>
+        <v>776921</v>
       </c>
       <c r="R3" t="n">
-        <v>7157628</v>
+        <v>7157641</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,11 +867,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-02</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>fertil!</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,32 +894,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128963916</v>
+        <v>128964083</v>
       </c>
       <c r="B4" t="n">
-        <v>91504</v>
+        <v>91540</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -936,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>776921</v>
+        <v>776887</v>
       </c>
       <c r="R4" t="n">
-        <v>7157641</v>
+        <v>7157655</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1107,7 +1107,7 @@
         <v>128964270</v>
       </c>
       <c r="B6" t="n">
-        <v>91992</v>
+        <v>91993</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>128963515</v>
       </c>
       <c r="B11" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1735,32 +1735,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128963423</v>
+        <v>128963275</v>
       </c>
       <c r="B12" t="n">
-        <v>91504</v>
+        <v>91540</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>777013</v>
+        <v>776991</v>
       </c>
       <c r="R12" t="n">
-        <v>7157604</v>
+        <v>7157610</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1840,32 +1840,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128963275</v>
+        <v>128963423</v>
       </c>
       <c r="B13" t="n">
-        <v>91540</v>
+        <v>91504</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1882,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>776991</v>
+        <v>777013</v>
       </c>
       <c r="R13" t="n">
-        <v>7157610</v>
+        <v>7157604</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1945,10 +1945,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128964198</v>
+        <v>128963824</v>
       </c>
       <c r="B14" t="n">
-        <v>91540</v>
+        <v>79041</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1956,29 +1956,25 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
@@ -1987,10 +1983,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>776862</v>
+        <v>776924</v>
       </c>
       <c r="R14" t="n">
-        <v>7157681</v>
+        <v>7157645</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2050,7 +2046,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128963824</v>
+        <v>128964345</v>
       </c>
       <c r="B15" t="n">
         <v>79041</v>
@@ -2079,7 +2075,11 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
@@ -2088,10 +2088,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>776924</v>
+        <v>776870</v>
       </c>
       <c r="R15" t="n">
-        <v>7157645</v>
+        <v>7157667</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2151,10 +2151,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128964345</v>
+        <v>128964198</v>
       </c>
       <c r="B16" t="n">
-        <v>79041</v>
+        <v>91540</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2162,27 +2162,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -2193,10 +2193,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>776870</v>
+        <v>776862</v>
       </c>
       <c r="R16" t="n">
-        <v>7157667</v>
+        <v>7157681</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2256,10 +2256,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128964180</v>
+        <v>128964055</v>
       </c>
       <c r="B17" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2267,30 +2267,31 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2298,10 +2299,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>776839</v>
+        <v>776909</v>
       </c>
       <c r="R17" t="n">
-        <v>7157679</v>
+        <v>7157645</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2336,13 +2337,17 @@
           <t>2025-10-02</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>hack i låga</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2466,42 +2471,41 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128963540</v>
+        <v>128964180</v>
       </c>
       <c r="B19" t="n">
-        <v>98704</v>
+        <v>79041</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2509,10 +2513,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>777003</v>
+        <v>776839</v>
       </c>
       <c r="R19" t="n">
-        <v>7157598</v>
+        <v>7157679</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2572,42 +2576,42 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128964055</v>
+        <v>128963540</v>
       </c>
       <c r="B20" t="n">
-        <v>57724</v>
+        <v>98705</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2615,10 +2619,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>776909</v>
+        <v>777003</v>
       </c>
       <c r="R20" t="n">
-        <v>7157645</v>
+        <v>7157598</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2653,17 +2657,13 @@
           <t>2025-10-02</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>hack i låga</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2895,7 +2895,7 @@
         <v>128963395</v>
       </c>
       <c r="B23" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3007,32 +3007,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128963073</v>
+        <v>128963189</v>
       </c>
       <c r="B24" t="n">
-        <v>82873</v>
+        <v>91504</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3049,10 +3049,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>776971</v>
+        <v>776995</v>
       </c>
       <c r="R24" t="n">
-        <v>7157600</v>
+        <v>7157615</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3112,32 +3112,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128963189</v>
+        <v>128963073</v>
       </c>
       <c r="B25" t="n">
-        <v>91504</v>
+        <v>82873</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3154,10 +3154,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>776995</v>
+        <v>776971</v>
       </c>
       <c r="R25" t="n">
-        <v>7157615</v>
+        <v>7157600</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3220,7 +3220,7 @@
         <v>128964193</v>
       </c>
       <c r="B26" t="n">
-        <v>91992</v>
+        <v>91993</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>128963472</v>
       </c>
       <c r="B27" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3433,10 +3433,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128963646</v>
+        <v>128963722</v>
       </c>
       <c r="B28" t="n">
-        <v>82873</v>
+        <v>91491</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3444,21 +3444,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1312</v>
+        <v>112</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3475,10 +3475,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>777005</v>
+        <v>776951</v>
       </c>
       <c r="R28" t="n">
-        <v>7157660</v>
+        <v>7157658</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3538,10 +3538,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128963722</v>
+        <v>128963646</v>
       </c>
       <c r="B29" t="n">
-        <v>91491</v>
+        <v>82873</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3549,21 +3549,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>112</v>
+        <v>1312</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3580,10 +3580,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>776951</v>
+        <v>777005</v>
       </c>
       <c r="R29" t="n">
-        <v>7157658</v>
+        <v>7157660</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3643,32 +3643,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128963102</v>
+        <v>128963560</v>
       </c>
       <c r="B30" t="n">
-        <v>91540</v>
+        <v>91504</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3685,10 +3685,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>776998</v>
+        <v>777002</v>
       </c>
       <c r="R30" t="n">
-        <v>7157616</v>
+        <v>7157629</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3748,7 +3748,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128964019</v>
+        <v>128963102</v>
       </c>
       <c r="B31" t="n">
         <v>91540</v>
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>776903</v>
+        <v>776998</v>
       </c>
       <c r="R31" t="n">
-        <v>7157641</v>
+        <v>7157616</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3853,32 +3853,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128963560</v>
+        <v>128964019</v>
       </c>
       <c r="B32" t="n">
-        <v>91504</v>
+        <v>91540</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3895,10 +3895,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>777002</v>
+        <v>776903</v>
       </c>
       <c r="R32" t="n">
-        <v>7157629</v>
+        <v>7157641</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4176,7 +4176,7 @@
         <v>128974745</v>
       </c>
       <c r="B35" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4193,14 +4193,10 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>

--- a/artfynd/A 46103-2025 artfynd.xlsx
+++ b/artfynd/A 46103-2025 artfynd.xlsx
@@ -675,45 +675,41 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128964143</v>
+        <v>128963916</v>
       </c>
       <c r="B2" t="n">
-        <v>79041</v>
+        <v>91504</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -721,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>776873</v>
+        <v>776921</v>
       </c>
       <c r="R2" t="n">
-        <v>7157628</v>
+        <v>7157641</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,11 +753,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-02</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>fertil!</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,32 +780,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128963916</v>
+        <v>128964083</v>
       </c>
       <c r="B3" t="n">
-        <v>91504</v>
+        <v>91540</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>776921</v>
+        <v>776887</v>
       </c>
       <c r="R3" t="n">
-        <v>7157641</v>
+        <v>7157655</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -894,10 +885,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128964083</v>
+        <v>128964143</v>
       </c>
       <c r="B4" t="n">
-        <v>91540</v>
+        <v>79041</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,30 +896,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -936,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>776887</v>
+        <v>776873</v>
       </c>
       <c r="R4" t="n">
-        <v>7157655</v>
+        <v>7157628</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,6 +967,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>fertil!</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1104,32 +1104,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128964270</v>
+        <v>128964110</v>
       </c>
       <c r="B6" t="n">
-        <v>91993</v>
+        <v>91491</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>112</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1146,10 +1146,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>776865</v>
+        <v>776877</v>
       </c>
       <c r="R6" t="n">
-        <v>7157670</v>
+        <v>7157631</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1209,7 +1209,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128964110</v>
+        <v>128963706</v>
       </c>
       <c r="B7" t="n">
         <v>91491</v>
@@ -1251,10 +1251,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>776877</v>
+        <v>776952</v>
       </c>
       <c r="R7" t="n">
-        <v>7157631</v>
+        <v>7157667</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,32 +1314,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128963706</v>
+        <v>128964270</v>
       </c>
       <c r="B8" t="n">
-        <v>91491</v>
+        <v>91993</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>112</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1356,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>776952</v>
+        <v>776865</v>
       </c>
       <c r="R8" t="n">
-        <v>7157667</v>
+        <v>7157670</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1632,7 +1632,7 @@
         <v>128963515</v>
       </c>
       <c r="B11" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1735,32 +1735,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128963275</v>
+        <v>128963423</v>
       </c>
       <c r="B12" t="n">
-        <v>91540</v>
+        <v>91504</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>776991</v>
+        <v>777013</v>
       </c>
       <c r="R12" t="n">
-        <v>7157610</v>
+        <v>7157604</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1840,32 +1840,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128963423</v>
+        <v>128963275</v>
       </c>
       <c r="B13" t="n">
-        <v>91504</v>
+        <v>91540</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1882,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>777013</v>
+        <v>776991</v>
       </c>
       <c r="R13" t="n">
-        <v>7157604</v>
+        <v>7157610</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1945,10 +1945,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128963824</v>
+        <v>128964198</v>
       </c>
       <c r="B14" t="n">
-        <v>79041</v>
+        <v>91540</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1956,25 +1956,29 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
@@ -1983,10 +1987,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>776924</v>
+        <v>776862</v>
       </c>
       <c r="R14" t="n">
-        <v>7157645</v>
+        <v>7157681</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2046,7 +2050,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128964345</v>
+        <v>128963824</v>
       </c>
       <c r="B15" t="n">
         <v>79041</v>
@@ -2075,11 +2079,7 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
@@ -2088,10 +2088,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>776870</v>
+        <v>776924</v>
       </c>
       <c r="R15" t="n">
-        <v>7157667</v>
+        <v>7157645</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2151,10 +2151,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128964198</v>
+        <v>128964345</v>
       </c>
       <c r="B16" t="n">
-        <v>91540</v>
+        <v>79041</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2162,27 +2162,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -2193,10 +2193,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>776862</v>
+        <v>776870</v>
       </c>
       <c r="R16" t="n">
-        <v>7157681</v>
+        <v>7157667</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2256,42 +2256,41 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128964055</v>
+        <v>128963674</v>
       </c>
       <c r="B17" t="n">
-        <v>57724</v>
+        <v>91504</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2299,10 +2298,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>776909</v>
+        <v>776962</v>
       </c>
       <c r="R17" t="n">
-        <v>7157645</v>
+        <v>7157631</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2337,17 +2336,13 @@
           <t>2025-10-02</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>hack i låga</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2366,38 +2361,38 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128963674</v>
+        <v>128964180</v>
       </c>
       <c r="B18" t="n">
-        <v>91504</v>
+        <v>79041</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -2408,10 +2403,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>776962</v>
+        <v>776839</v>
       </c>
       <c r="R18" t="n">
-        <v>7157631</v>
+        <v>7157679</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2471,10 +2466,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128964180</v>
+        <v>128964055</v>
       </c>
       <c r="B19" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2482,30 +2477,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2513,10 +2509,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>776839</v>
+        <v>776909</v>
       </c>
       <c r="R19" t="n">
-        <v>7157679</v>
+        <v>7157645</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2551,13 +2547,17 @@
           <t>2025-10-02</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>hack i låga</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2579,7 +2579,7 @@
         <v>128963540</v>
       </c>
       <c r="B20" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>128963395</v>
       </c>
       <c r="B23" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>128963472</v>
       </c>
       <c r="B27" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3643,32 +3643,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128963560</v>
+        <v>128963102</v>
       </c>
       <c r="B30" t="n">
-        <v>91504</v>
+        <v>91540</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3685,10 +3685,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>777002</v>
+        <v>776998</v>
       </c>
       <c r="R30" t="n">
-        <v>7157629</v>
+        <v>7157616</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3748,7 +3748,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128963102</v>
+        <v>128964019</v>
       </c>
       <c r="B31" t="n">
         <v>91540</v>
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>776998</v>
+        <v>776903</v>
       </c>
       <c r="R31" t="n">
-        <v>7157616</v>
+        <v>7157641</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3853,32 +3853,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128964019</v>
+        <v>128963560</v>
       </c>
       <c r="B32" t="n">
-        <v>91540</v>
+        <v>91504</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3895,10 +3895,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>776903</v>
+        <v>777002</v>
       </c>
       <c r="R32" t="n">
-        <v>7157641</v>
+        <v>7157629</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>

--- a/artfynd/A 46103-2025 artfynd.xlsx
+++ b/artfynd/A 46103-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128963916</v>
       </c>
       <c r="B2" t="n">
-        <v>91504</v>
+        <v>91507</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>128964083</v>
       </c>
       <c r="B3" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>128964143</v>
       </c>
       <c r="B4" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>128963639</v>
       </c>
       <c r="B5" t="n">
-        <v>82873</v>
+        <v>82877</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1104,32 +1104,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128964110</v>
+        <v>128964270</v>
       </c>
       <c r="B6" t="n">
-        <v>91491</v>
+        <v>91996</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>112</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1146,10 +1146,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>776877</v>
+        <v>776865</v>
       </c>
       <c r="R6" t="n">
-        <v>7157631</v>
+        <v>7157670</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1209,10 +1209,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128963706</v>
+        <v>128964110</v>
       </c>
       <c r="B7" t="n">
-        <v>91491</v>
+        <v>91494</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,10 +1251,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>776952</v>
+        <v>776877</v>
       </c>
       <c r="R7" t="n">
-        <v>7157667</v>
+        <v>7157631</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,32 +1314,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128964270</v>
+        <v>128963706</v>
       </c>
       <c r="B8" t="n">
-        <v>91993</v>
+        <v>91494</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>112</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1356,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>776865</v>
+        <v>776952</v>
       </c>
       <c r="R8" t="n">
-        <v>7157670</v>
+        <v>7157667</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,7 +1422,7 @@
         <v>128963556</v>
       </c>
       <c r="B9" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>128964297</v>
       </c>
       <c r="B10" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>128963515</v>
       </c>
       <c r="B11" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1735,32 +1735,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128963423</v>
+        <v>128963275</v>
       </c>
       <c r="B12" t="n">
-        <v>91504</v>
+        <v>91543</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>777013</v>
+        <v>776991</v>
       </c>
       <c r="R12" t="n">
-        <v>7157604</v>
+        <v>7157610</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1840,32 +1840,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128963275</v>
+        <v>128963423</v>
       </c>
       <c r="B13" t="n">
-        <v>91540</v>
+        <v>91507</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1882,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>776991</v>
+        <v>777013</v>
       </c>
       <c r="R13" t="n">
-        <v>7157610</v>
+        <v>7157604</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1948,7 +1948,7 @@
         <v>128964198</v>
       </c>
       <c r="B14" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>128963824</v>
       </c>
       <c r="B15" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>128964345</v>
       </c>
       <c r="B16" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
         <v>128963674</v>
       </c>
       <c r="B17" t="n">
-        <v>91504</v>
+        <v>91507</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>128964180</v>
       </c>
       <c r="B18" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>128963540</v>
       </c>
       <c r="B20" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2685,7 +2685,7 @@
         <v>128964009</v>
       </c>
       <c r="B21" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2790,7 +2790,7 @@
         <v>128964410</v>
       </c>
       <c r="B22" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>128963395</v>
       </c>
       <c r="B23" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3007,32 +3007,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128963189</v>
+        <v>128963073</v>
       </c>
       <c r="B24" t="n">
-        <v>91504</v>
+        <v>82877</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3049,10 +3049,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>776995</v>
+        <v>776971</v>
       </c>
       <c r="R24" t="n">
-        <v>7157615</v>
+        <v>7157600</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3112,32 +3112,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128963073</v>
+        <v>128963189</v>
       </c>
       <c r="B25" t="n">
-        <v>82873</v>
+        <v>91507</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3154,10 +3154,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>776971</v>
+        <v>776995</v>
       </c>
       <c r="R25" t="n">
-        <v>7157600</v>
+        <v>7157615</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3217,10 +3217,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128964193</v>
+        <v>128963472</v>
       </c>
       <c r="B26" t="n">
-        <v>91993</v>
+        <v>98710</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3228,30 +3228,31 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3259,10 +3260,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>776862</v>
+        <v>777013</v>
       </c>
       <c r="R26" t="n">
-        <v>7157681</v>
+        <v>7157601</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3295,6 +3296,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>ca 2 x 2 meter med bladrosetter!</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3322,10 +3328,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128963472</v>
+        <v>128964193</v>
       </c>
       <c r="B27" t="n">
-        <v>98706</v>
+        <v>91996</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3333,31 +3339,30 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3365,10 +3370,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>777013</v>
+        <v>776862</v>
       </c>
       <c r="R27" t="n">
-        <v>7157601</v>
+        <v>7157681</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3401,11 +3406,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-02</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>ca 2 x 2 meter med bladrosetter!</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3433,10 +3433,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128963722</v>
+        <v>128963646</v>
       </c>
       <c r="B28" t="n">
-        <v>91491</v>
+        <v>82877</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3444,21 +3444,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>112</v>
+        <v>1312</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3475,10 +3475,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>776951</v>
+        <v>777005</v>
       </c>
       <c r="R28" t="n">
-        <v>7157658</v>
+        <v>7157660</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3538,10 +3538,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128963646</v>
+        <v>128963722</v>
       </c>
       <c r="B29" t="n">
-        <v>82873</v>
+        <v>91494</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3549,21 +3549,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1312</v>
+        <v>112</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3580,10 +3580,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>777005</v>
+        <v>776951</v>
       </c>
       <c r="R29" t="n">
-        <v>7157660</v>
+        <v>7157658</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3643,32 +3643,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128963102</v>
+        <v>128963560</v>
       </c>
       <c r="B30" t="n">
-        <v>91540</v>
+        <v>91507</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3685,10 +3685,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>776998</v>
+        <v>777002</v>
       </c>
       <c r="R30" t="n">
-        <v>7157616</v>
+        <v>7157629</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3748,10 +3748,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128964019</v>
+        <v>128963102</v>
       </c>
       <c r="B31" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>776903</v>
+        <v>776998</v>
       </c>
       <c r="R31" t="n">
-        <v>7157641</v>
+        <v>7157616</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3853,32 +3853,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128963560</v>
+        <v>128964019</v>
       </c>
       <c r="B32" t="n">
-        <v>91504</v>
+        <v>91543</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3895,10 +3895,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>777002</v>
+        <v>776903</v>
       </c>
       <c r="R32" t="n">
-        <v>7157629</v>
+        <v>7157641</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4071,7 +4071,7 @@
         <v>128974663</v>
       </c>
       <c r="B34" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>128974745</v>
       </c>
       <c r="B35" t="n">
-        <v>91560</v>
+        <v>91563</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         <v>128973835</v>
       </c>
       <c r="B36" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 46103-2025 artfynd.xlsx
+++ b/artfynd/A 46103-2025 artfynd.xlsx
@@ -1524,41 +1524,42 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128964297</v>
+        <v>128963515</v>
       </c>
       <c r="B10" t="n">
-        <v>91543</v>
+        <v>98710</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1566,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>776865</v>
+        <v>777009</v>
       </c>
       <c r="R10" t="n">
-        <v>7157670</v>
+        <v>7157591</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,42 +1630,41 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128963515</v>
+        <v>128964297</v>
       </c>
       <c r="B11" t="n">
-        <v>98710</v>
+        <v>91543</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1672,10 +1672,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>777009</v>
+        <v>776865</v>
       </c>
       <c r="R11" t="n">
-        <v>7157591</v>
+        <v>7157670</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -3433,10 +3433,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128963646</v>
+        <v>128963722</v>
       </c>
       <c r="B28" t="n">
-        <v>82877</v>
+        <v>91494</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3444,21 +3444,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1312</v>
+        <v>112</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3475,10 +3475,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>777005</v>
+        <v>776951</v>
       </c>
       <c r="R28" t="n">
-        <v>7157660</v>
+        <v>7157658</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3538,10 +3538,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128963722</v>
+        <v>128963646</v>
       </c>
       <c r="B29" t="n">
-        <v>91494</v>
+        <v>82877</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3549,21 +3549,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>112</v>
+        <v>1312</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3580,10 +3580,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>776951</v>
+        <v>777005</v>
       </c>
       <c r="R29" t="n">
-        <v>7157658</v>
+        <v>7157660</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>

--- a/artfynd/A 46103-2025 artfynd.xlsx
+++ b/artfynd/A 46103-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128963916</v>
+        <v>128964083</v>
       </c>
       <c r="B2" t="n">
-        <v>91507</v>
+        <v>91545</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -717,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>776921</v>
+        <v>776887</v>
       </c>
       <c r="R2" t="n">
-        <v>7157641</v>
+        <v>7157655</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -780,32 +780,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128964083</v>
+        <v>128963916</v>
       </c>
       <c r="B3" t="n">
-        <v>91543</v>
+        <v>91509</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>776887</v>
+        <v>776921</v>
       </c>
       <c r="R3" t="n">
-        <v>7157655</v>
+        <v>7157641</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,7 +888,7 @@
         <v>128964143</v>
       </c>
       <c r="B4" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>128963639</v>
       </c>
       <c r="B5" t="n">
-        <v>82877</v>
+        <v>82878</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1104,32 +1104,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128964270</v>
+        <v>128964110</v>
       </c>
       <c r="B6" t="n">
-        <v>91996</v>
+        <v>91496</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>112</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1146,10 +1146,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>776865</v>
+        <v>776877</v>
       </c>
       <c r="R6" t="n">
-        <v>7157670</v>
+        <v>7157631</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1209,10 +1209,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128964110</v>
+        <v>128963706</v>
       </c>
       <c r="B7" t="n">
-        <v>91494</v>
+        <v>91496</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,10 +1251,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>776877</v>
+        <v>776952</v>
       </c>
       <c r="R7" t="n">
-        <v>7157631</v>
+        <v>7157667</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,32 +1314,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128963706</v>
+        <v>128964270</v>
       </c>
       <c r="B8" t="n">
-        <v>91494</v>
+        <v>91998</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>112</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1356,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>776952</v>
+        <v>776865</v>
       </c>
       <c r="R8" t="n">
-        <v>7157667</v>
+        <v>7157670</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,7 +1422,7 @@
         <v>128963556</v>
       </c>
       <c r="B9" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1524,42 +1524,41 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128963515</v>
+        <v>128964297</v>
       </c>
       <c r="B10" t="n">
-        <v>98710</v>
+        <v>91545</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1567,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>777009</v>
+        <v>776865</v>
       </c>
       <c r="R10" t="n">
-        <v>7157591</v>
+        <v>7157670</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1630,41 +1629,42 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128964297</v>
+        <v>128963515</v>
       </c>
       <c r="B11" t="n">
-        <v>91543</v>
+        <v>98712</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1672,10 +1672,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>776865</v>
+        <v>777009</v>
       </c>
       <c r="R11" t="n">
-        <v>7157670</v>
+        <v>7157591</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1738,7 +1738,7 @@
         <v>128963275</v>
       </c>
       <c r="B12" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>128963423</v>
       </c>
       <c r="B13" t="n">
-        <v>91507</v>
+        <v>91509</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1945,10 +1945,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128964198</v>
+        <v>128963824</v>
       </c>
       <c r="B14" t="n">
-        <v>91543</v>
+        <v>79044</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1956,29 +1956,25 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
@@ -1987,10 +1983,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>776862</v>
+        <v>776924</v>
       </c>
       <c r="R14" t="n">
-        <v>7157681</v>
+        <v>7157645</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2050,10 +2046,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128963824</v>
+        <v>128964345</v>
       </c>
       <c r="B15" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2079,7 +2075,11 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
@@ -2088,10 +2088,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>776924</v>
+        <v>776870</v>
       </c>
       <c r="R15" t="n">
-        <v>7157645</v>
+        <v>7157667</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2151,10 +2151,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128964345</v>
+        <v>128964198</v>
       </c>
       <c r="B16" t="n">
-        <v>79043</v>
+        <v>91545</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2162,27 +2162,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -2193,10 +2193,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>776870</v>
+        <v>776862</v>
       </c>
       <c r="R16" t="n">
-        <v>7157667</v>
+        <v>7157681</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2256,41 +2256,42 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128963674</v>
+        <v>128964055</v>
       </c>
       <c r="B17" t="n">
-        <v>91507</v>
+        <v>57724</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2298,10 +2299,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>776962</v>
+        <v>776909</v>
       </c>
       <c r="R17" t="n">
-        <v>7157631</v>
+        <v>7157645</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2336,13 +2337,17 @@
           <t>2025-10-02</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>hack i låga</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2361,38 +2366,38 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128964180</v>
+        <v>128963674</v>
       </c>
       <c r="B18" t="n">
-        <v>79043</v>
+        <v>91509</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -2403,10 +2408,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>776839</v>
+        <v>776962</v>
       </c>
       <c r="R18" t="n">
-        <v>7157679</v>
+        <v>7157631</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2466,10 +2471,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128964055</v>
+        <v>128964180</v>
       </c>
       <c r="B19" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2477,31 +2482,30 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2509,10 +2513,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>776909</v>
+        <v>776839</v>
       </c>
       <c r="R19" t="n">
-        <v>7157645</v>
+        <v>7157679</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2547,17 +2551,13 @@
           <t>2025-10-02</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>hack i låga</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2579,7 +2579,7 @@
         <v>128963540</v>
       </c>
       <c r="B20" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2685,7 +2685,7 @@
         <v>128964009</v>
       </c>
       <c r="B21" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2790,7 +2790,7 @@
         <v>128964410</v>
       </c>
       <c r="B22" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>128963395</v>
       </c>
       <c r="B23" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3010,7 +3010,7 @@
         <v>128963073</v>
       </c>
       <c r="B24" t="n">
-        <v>82877</v>
+        <v>82878</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         <v>128963189</v>
       </c>
       <c r="B25" t="n">
-        <v>91507</v>
+        <v>91509</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3217,10 +3217,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128963472</v>
+        <v>128964193</v>
       </c>
       <c r="B26" t="n">
-        <v>98710</v>
+        <v>91998</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3228,31 +3228,30 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3260,10 +3259,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>777013</v>
+        <v>776862</v>
       </c>
       <c r="R26" t="n">
-        <v>7157601</v>
+        <v>7157681</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3296,11 +3295,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-02</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>ca 2 x 2 meter med bladrosetter!</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3328,10 +3322,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128964193</v>
+        <v>128963472</v>
       </c>
       <c r="B27" t="n">
-        <v>91996</v>
+        <v>98712</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3339,30 +3333,31 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3370,10 +3365,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>776862</v>
+        <v>777013</v>
       </c>
       <c r="R27" t="n">
-        <v>7157681</v>
+        <v>7157601</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3406,6 +3401,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>ca 2 x 2 meter med bladrosetter!</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3436,7 +3436,7 @@
         <v>128963722</v>
       </c>
       <c r="B28" t="n">
-        <v>91494</v>
+        <v>91496</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3541,7 +3541,7 @@
         <v>128963646</v>
       </c>
       <c r="B29" t="n">
-        <v>82877</v>
+        <v>82878</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3643,32 +3643,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128963560</v>
+        <v>128963102</v>
       </c>
       <c r="B30" t="n">
-        <v>91507</v>
+        <v>91545</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3685,10 +3685,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>777002</v>
+        <v>776998</v>
       </c>
       <c r="R30" t="n">
-        <v>7157629</v>
+        <v>7157616</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3748,10 +3748,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128963102</v>
+        <v>128964019</v>
       </c>
       <c r="B31" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>776998</v>
+        <v>776903</v>
       </c>
       <c r="R31" t="n">
-        <v>7157616</v>
+        <v>7157641</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3853,32 +3853,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128964019</v>
+        <v>128963560</v>
       </c>
       <c r="B32" t="n">
-        <v>91543</v>
+        <v>91509</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3895,10 +3895,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>776903</v>
+        <v>777002</v>
       </c>
       <c r="R32" t="n">
-        <v>7157641</v>
+        <v>7157629</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4071,7 +4071,7 @@
         <v>128974663</v>
       </c>
       <c r="B34" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>128974745</v>
       </c>
       <c r="B35" t="n">
-        <v>91563</v>
+        <v>91565</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         <v>128973835</v>
       </c>
       <c r="B36" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 46103-2025 artfynd.xlsx
+++ b/artfynd/A 46103-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128964083</v>
       </c>
       <c r="B2" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,41 +780,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128963916</v>
+        <v>128964143</v>
       </c>
       <c r="B3" t="n">
-        <v>91509</v>
+        <v>79044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -822,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>776921</v>
+        <v>776873</v>
       </c>
       <c r="R3" t="n">
-        <v>7157641</v>
+        <v>7157628</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,6 +862,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>fertil!</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,45 +894,41 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128964143</v>
+        <v>128963916</v>
       </c>
       <c r="B4" t="n">
-        <v>79044</v>
+        <v>91513</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -931,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>776873</v>
+        <v>776921</v>
       </c>
       <c r="R4" t="n">
-        <v>7157628</v>
+        <v>7157641</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -967,11 +972,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-02</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>fertil!</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1104,32 +1104,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128964110</v>
+        <v>128964270</v>
       </c>
       <c r="B6" t="n">
-        <v>91496</v>
+        <v>92002</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>112</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1146,10 +1146,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>776877</v>
+        <v>776865</v>
       </c>
       <c r="R6" t="n">
-        <v>7157631</v>
+        <v>7157670</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1209,10 +1209,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128963706</v>
+        <v>128964110</v>
       </c>
       <c r="B7" t="n">
-        <v>91496</v>
+        <v>91500</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,10 +1251,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>776952</v>
+        <v>776877</v>
       </c>
       <c r="R7" t="n">
-        <v>7157667</v>
+        <v>7157631</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,32 +1314,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128964270</v>
+        <v>128963706</v>
       </c>
       <c r="B8" t="n">
-        <v>91998</v>
+        <v>91500</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>112</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1356,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>776865</v>
+        <v>776952</v>
       </c>
       <c r="R8" t="n">
-        <v>7157670</v>
+        <v>7157667</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,7 +1422,7 @@
         <v>128963556</v>
       </c>
       <c r="B9" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>128964297</v>
       </c>
       <c r="B10" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>128963515</v>
       </c>
       <c r="B11" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>128963275</v>
       </c>
       <c r="B12" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>128963423</v>
       </c>
       <c r="B13" t="n">
-        <v>91509</v>
+        <v>91513</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1945,10 +1945,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128963824</v>
+        <v>128964198</v>
       </c>
       <c r="B14" t="n">
-        <v>79044</v>
+        <v>91549</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1956,25 +1956,29 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
@@ -1983,10 +1987,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>776924</v>
+        <v>776862</v>
       </c>
       <c r="R14" t="n">
-        <v>7157645</v>
+        <v>7157681</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2046,7 +2050,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128964345</v>
+        <v>128963824</v>
       </c>
       <c r="B15" t="n">
         <v>79044</v>
@@ -2075,11 +2079,7 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
@@ -2088,10 +2088,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>776870</v>
+        <v>776924</v>
       </c>
       <c r="R15" t="n">
-        <v>7157667</v>
+        <v>7157645</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2151,10 +2151,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128964198</v>
+        <v>128964345</v>
       </c>
       <c r="B16" t="n">
-        <v>91545</v>
+        <v>79044</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2162,27 +2162,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -2193,10 +2193,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>776862</v>
+        <v>776870</v>
       </c>
       <c r="R16" t="n">
-        <v>7157681</v>
+        <v>7157667</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2256,42 +2256,42 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128964055</v>
+        <v>128963540</v>
       </c>
       <c r="B17" t="n">
-        <v>57724</v>
+        <v>98716</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2299,10 +2299,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>776909</v>
+        <v>777003</v>
       </c>
       <c r="R17" t="n">
-        <v>7157645</v>
+        <v>7157598</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2337,17 +2337,13 @@
           <t>2025-10-02</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>hack i låga</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2366,38 +2362,38 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128963674</v>
+        <v>128964180</v>
       </c>
       <c r="B18" t="n">
-        <v>91509</v>
+        <v>79044</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -2408,10 +2404,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>776962</v>
+        <v>776839</v>
       </c>
       <c r="R18" t="n">
-        <v>7157631</v>
+        <v>7157679</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2471,38 +2467,38 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128964180</v>
+        <v>128963674</v>
       </c>
       <c r="B19" t="n">
-        <v>79044</v>
+        <v>91513</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -2513,10 +2509,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>776839</v>
+        <v>776962</v>
       </c>
       <c r="R19" t="n">
-        <v>7157679</v>
+        <v>7157631</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2576,42 +2572,42 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128963540</v>
+        <v>128964055</v>
       </c>
       <c r="B20" t="n">
-        <v>98712</v>
+        <v>57724</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2619,10 +2615,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>777003</v>
+        <v>776909</v>
       </c>
       <c r="R20" t="n">
-        <v>7157598</v>
+        <v>7157645</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2657,13 +2653,17 @@
           <t>2025-10-02</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>hack i låga</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2790,7 +2790,7 @@
         <v>128964410</v>
       </c>
       <c r="B22" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>128963395</v>
       </c>
       <c r="B23" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         <v>128963189</v>
       </c>
       <c r="B25" t="n">
-        <v>91509</v>
+        <v>91513</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>128964193</v>
       </c>
       <c r="B26" t="n">
-        <v>91998</v>
+        <v>92002</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>128963472</v>
       </c>
       <c r="B27" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3433,10 +3433,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128963722</v>
+        <v>128963646</v>
       </c>
       <c r="B28" t="n">
-        <v>91496</v>
+        <v>82878</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3444,21 +3444,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>112</v>
+        <v>1312</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3475,10 +3475,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>776951</v>
+        <v>777005</v>
       </c>
       <c r="R28" t="n">
-        <v>7157658</v>
+        <v>7157660</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3538,10 +3538,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128963646</v>
+        <v>128963722</v>
       </c>
       <c r="B29" t="n">
-        <v>82878</v>
+        <v>91500</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3549,21 +3549,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1312</v>
+        <v>112</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3580,10 +3580,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>777005</v>
+        <v>776951</v>
       </c>
       <c r="R29" t="n">
-        <v>7157660</v>
+        <v>7157658</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3643,32 +3643,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128963102</v>
+        <v>128963560</v>
       </c>
       <c r="B30" t="n">
-        <v>91545</v>
+        <v>91513</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3685,10 +3685,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>776998</v>
+        <v>777002</v>
       </c>
       <c r="R30" t="n">
-        <v>7157616</v>
+        <v>7157629</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3748,10 +3748,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128964019</v>
+        <v>128963102</v>
       </c>
       <c r="B31" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>776903</v>
+        <v>776998</v>
       </c>
       <c r="R31" t="n">
-        <v>7157641</v>
+        <v>7157616</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3853,32 +3853,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128963560</v>
+        <v>128964019</v>
       </c>
       <c r="B32" t="n">
-        <v>91509</v>
+        <v>91549</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3895,10 +3895,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>777002</v>
+        <v>776903</v>
       </c>
       <c r="R32" t="n">
-        <v>7157629</v>
+        <v>7157641</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4176,7 +4176,7 @@
         <v>128974745</v>
       </c>
       <c r="B35" t="n">
-        <v>91565</v>
+        <v>91569</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 46103-2025 artfynd.xlsx
+++ b/artfynd/A 46103-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128964083</v>
       </c>
       <c r="B2" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,45 +780,41 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128964143</v>
+        <v>128963916</v>
       </c>
       <c r="B3" t="n">
-        <v>79044</v>
+        <v>91514</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -826,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>776873</v>
+        <v>776921</v>
       </c>
       <c r="R3" t="n">
-        <v>7157628</v>
+        <v>7157641</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-02</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>fertil!</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,41 +885,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128963916</v>
+        <v>128964143</v>
       </c>
       <c r="B4" t="n">
-        <v>91513</v>
+        <v>79044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -936,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>776921</v>
+        <v>776873</v>
       </c>
       <c r="R4" t="n">
-        <v>7157641</v>
+        <v>7157628</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,6 +967,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>fertil!</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1107,7 +1107,7 @@
         <v>128964270</v>
       </c>
       <c r="B6" t="n">
-        <v>92002</v>
+        <v>92003</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>128964110</v>
       </c>
       <c r="B7" t="n">
-        <v>91500</v>
+        <v>91501</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>128963706</v>
       </c>
       <c r="B8" t="n">
-        <v>91500</v>
+        <v>91501</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1422,7 +1422,7 @@
         <v>128963556</v>
       </c>
       <c r="B9" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>128964297</v>
       </c>
       <c r="B10" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>128963515</v>
       </c>
       <c r="B11" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1735,32 +1735,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128963275</v>
+        <v>128963423</v>
       </c>
       <c r="B12" t="n">
-        <v>91549</v>
+        <v>91514</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>776991</v>
+        <v>777013</v>
       </c>
       <c r="R12" t="n">
-        <v>7157610</v>
+        <v>7157604</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1840,32 +1840,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128963423</v>
+        <v>128963275</v>
       </c>
       <c r="B13" t="n">
-        <v>91513</v>
+        <v>91550</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1882,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>777013</v>
+        <v>776991</v>
       </c>
       <c r="R13" t="n">
-        <v>7157604</v>
+        <v>7157610</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1945,10 +1945,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128964198</v>
+        <v>128963824</v>
       </c>
       <c r="B14" t="n">
-        <v>91549</v>
+        <v>79044</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1956,29 +1956,25 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
@@ -1987,10 +1983,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>776862</v>
+        <v>776924</v>
       </c>
       <c r="R14" t="n">
-        <v>7157681</v>
+        <v>7157645</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2050,7 +2046,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128963824</v>
+        <v>128964345</v>
       </c>
       <c r="B15" t="n">
         <v>79044</v>
@@ -2079,7 +2075,11 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
@@ -2088,10 +2088,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>776924</v>
+        <v>776870</v>
       </c>
       <c r="R15" t="n">
-        <v>7157645</v>
+        <v>7157667</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2151,10 +2151,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128964345</v>
+        <v>128964198</v>
       </c>
       <c r="B16" t="n">
-        <v>79044</v>
+        <v>91550</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2162,27 +2162,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -2193,10 +2193,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>776870</v>
+        <v>776862</v>
       </c>
       <c r="R16" t="n">
-        <v>7157667</v>
+        <v>7157681</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2256,42 +2256,42 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128963540</v>
+        <v>128964055</v>
       </c>
       <c r="B17" t="n">
-        <v>98716</v>
+        <v>57724</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2299,10 +2299,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>777003</v>
+        <v>776909</v>
       </c>
       <c r="R17" t="n">
-        <v>7157598</v>
+        <v>7157645</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2337,13 +2337,17 @@
           <t>2025-10-02</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>hack i låga</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2362,41 +2366,42 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128964180</v>
+        <v>128963540</v>
       </c>
       <c r="B18" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2404,10 +2409,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>776839</v>
+        <v>777003</v>
       </c>
       <c r="R18" t="n">
-        <v>7157679</v>
+        <v>7157598</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2470,7 +2475,7 @@
         <v>128963674</v>
       </c>
       <c r="B19" t="n">
-        <v>91513</v>
+        <v>91514</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2572,10 +2577,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128964055</v>
+        <v>128964180</v>
       </c>
       <c r="B20" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2583,31 +2588,30 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2615,10 +2619,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>776909</v>
+        <v>776839</v>
       </c>
       <c r="R20" t="n">
-        <v>7157645</v>
+        <v>7157679</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2653,17 +2657,13 @@
           <t>2025-10-02</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>hack i låga</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2790,7 +2790,7 @@
         <v>128964410</v>
       </c>
       <c r="B22" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>128963395</v>
       </c>
       <c r="B23" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         <v>128963189</v>
       </c>
       <c r="B25" t="n">
-        <v>91513</v>
+        <v>91514</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3217,10 +3217,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128964193</v>
+        <v>128963472</v>
       </c>
       <c r="B26" t="n">
-        <v>92002</v>
+        <v>98724</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3228,30 +3228,31 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3259,10 +3260,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>776862</v>
+        <v>777013</v>
       </c>
       <c r="R26" t="n">
-        <v>7157681</v>
+        <v>7157601</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3295,6 +3296,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>ca 2 x 2 meter med bladrosetter!</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3322,10 +3328,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128963472</v>
+        <v>128964193</v>
       </c>
       <c r="B27" t="n">
-        <v>98716</v>
+        <v>92003</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3333,31 +3339,30 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3365,10 +3370,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>777013</v>
+        <v>776862</v>
       </c>
       <c r="R27" t="n">
-        <v>7157601</v>
+        <v>7157681</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3401,11 +3406,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-02</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>ca 2 x 2 meter med bladrosetter!</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3541,7 +3541,7 @@
         <v>128963722</v>
       </c>
       <c r="B29" t="n">
-        <v>91500</v>
+        <v>91501</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3643,32 +3643,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128963560</v>
+        <v>128963102</v>
       </c>
       <c r="B30" t="n">
-        <v>91513</v>
+        <v>91550</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3685,10 +3685,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>777002</v>
+        <v>776998</v>
       </c>
       <c r="R30" t="n">
-        <v>7157629</v>
+        <v>7157616</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3748,10 +3748,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128963102</v>
+        <v>128964019</v>
       </c>
       <c r="B31" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>776998</v>
+        <v>776903</v>
       </c>
       <c r="R31" t="n">
-        <v>7157616</v>
+        <v>7157641</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3853,32 +3853,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128964019</v>
+        <v>128963560</v>
       </c>
       <c r="B32" t="n">
-        <v>91549</v>
+        <v>91514</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3895,10 +3895,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>776903</v>
+        <v>777002</v>
       </c>
       <c r="R32" t="n">
-        <v>7157641</v>
+        <v>7157629</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4176,7 +4176,7 @@
         <v>128974745</v>
       </c>
       <c r="B35" t="n">
-        <v>91569</v>
+        <v>91570</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 46103-2025 artfynd.xlsx
+++ b/artfynd/A 46103-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128964083</v>
+        <v>128964143</v>
       </c>
       <c r="B2" t="n">
-        <v>91550</v>
+        <v>79044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,30 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -717,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>776887</v>
+        <v>776873</v>
       </c>
       <c r="R2" t="n">
-        <v>7157655</v>
+        <v>7157628</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,6 +757,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>fertil!</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,32 +789,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128963916</v>
+        <v>128964083</v>
       </c>
       <c r="B3" t="n">
-        <v>91514</v>
+        <v>91550</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>776921</v>
+        <v>776887</v>
       </c>
       <c r="R3" t="n">
-        <v>7157641</v>
+        <v>7157655</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,45 +894,41 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128964143</v>
+        <v>128963916</v>
       </c>
       <c r="B4" t="n">
-        <v>79044</v>
+        <v>91514</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -931,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>776873</v>
+        <v>776921</v>
       </c>
       <c r="R4" t="n">
-        <v>7157628</v>
+        <v>7157641</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -967,11 +972,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-02</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>fertil!</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1104,32 +1104,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128964270</v>
+        <v>128964110</v>
       </c>
       <c r="B6" t="n">
-        <v>92003</v>
+        <v>91501</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>112</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1146,10 +1146,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>776865</v>
+        <v>776877</v>
       </c>
       <c r="R6" t="n">
-        <v>7157670</v>
+        <v>7157631</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1209,7 +1209,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128964110</v>
+        <v>128963706</v>
       </c>
       <c r="B7" t="n">
         <v>91501</v>
@@ -1251,10 +1251,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>776877</v>
+        <v>776952</v>
       </c>
       <c r="R7" t="n">
-        <v>7157631</v>
+        <v>7157667</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,32 +1314,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128963706</v>
+        <v>128964270</v>
       </c>
       <c r="B8" t="n">
-        <v>91501</v>
+        <v>92003</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>112</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1356,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>776952</v>
+        <v>776865</v>
       </c>
       <c r="R8" t="n">
-        <v>7157667</v>
+        <v>7157670</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1524,41 +1524,42 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128964297</v>
+        <v>128963515</v>
       </c>
       <c r="B10" t="n">
-        <v>91550</v>
+        <v>98724</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1566,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>776865</v>
+        <v>777009</v>
       </c>
       <c r="R10" t="n">
-        <v>7157670</v>
+        <v>7157591</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,42 +1630,41 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128963515</v>
+        <v>128964297</v>
       </c>
       <c r="B11" t="n">
-        <v>98724</v>
+        <v>91550</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1672,10 +1672,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>777009</v>
+        <v>776865</v>
       </c>
       <c r="R11" t="n">
-        <v>7157591</v>
+        <v>7157670</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,32 +1735,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128963423</v>
+        <v>128963275</v>
       </c>
       <c r="B12" t="n">
-        <v>91514</v>
+        <v>91550</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>777013</v>
+        <v>776991</v>
       </c>
       <c r="R12" t="n">
-        <v>7157604</v>
+        <v>7157610</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1840,32 +1840,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128963275</v>
+        <v>128963423</v>
       </c>
       <c r="B13" t="n">
-        <v>91550</v>
+        <v>91514</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1882,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>776991</v>
+        <v>777013</v>
       </c>
       <c r="R13" t="n">
-        <v>7157610</v>
+        <v>7157604</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2256,42 +2256,41 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128964055</v>
+        <v>128963674</v>
       </c>
       <c r="B17" t="n">
-        <v>57724</v>
+        <v>91514</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2299,10 +2298,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>776909</v>
+        <v>776962</v>
       </c>
       <c r="R17" t="n">
-        <v>7157645</v>
+        <v>7157631</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2337,17 +2336,13 @@
           <t>2025-10-02</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>hack i låga</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2366,42 +2361,41 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128963540</v>
+        <v>128964180</v>
       </c>
       <c r="B18" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2409,10 +2403,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>777003</v>
+        <v>776839</v>
       </c>
       <c r="R18" t="n">
-        <v>7157598</v>
+        <v>7157679</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2472,41 +2466,42 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128963674</v>
+        <v>128964055</v>
       </c>
       <c r="B19" t="n">
-        <v>91514</v>
+        <v>57724</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2514,10 +2509,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>776962</v>
+        <v>776909</v>
       </c>
       <c r="R19" t="n">
-        <v>7157631</v>
+        <v>7157645</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2552,13 +2547,17 @@
           <t>2025-10-02</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>hack i låga</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2577,41 +2576,42 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128964180</v>
+        <v>128963540</v>
       </c>
       <c r="B20" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2619,10 +2619,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>776839</v>
+        <v>777003</v>
       </c>
       <c r="R20" t="n">
-        <v>7157679</v>
+        <v>7157598</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3007,32 +3007,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128963073</v>
+        <v>128963189</v>
       </c>
       <c r="B24" t="n">
-        <v>82878</v>
+        <v>91514</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3049,10 +3049,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>776971</v>
+        <v>776995</v>
       </c>
       <c r="R24" t="n">
-        <v>7157600</v>
+        <v>7157615</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3112,32 +3112,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128963189</v>
+        <v>128963073</v>
       </c>
       <c r="B25" t="n">
-        <v>91514</v>
+        <v>82878</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3154,10 +3154,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>776995</v>
+        <v>776971</v>
       </c>
       <c r="R25" t="n">
-        <v>7157615</v>
+        <v>7157600</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3217,10 +3217,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128963472</v>
+        <v>128964193</v>
       </c>
       <c r="B26" t="n">
-        <v>98724</v>
+        <v>92003</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3228,31 +3228,30 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3260,10 +3259,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>777013</v>
+        <v>776862</v>
       </c>
       <c r="R26" t="n">
-        <v>7157601</v>
+        <v>7157681</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3296,11 +3295,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-02</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>ca 2 x 2 meter med bladrosetter!</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3328,10 +3322,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128964193</v>
+        <v>128963472</v>
       </c>
       <c r="B27" t="n">
-        <v>92003</v>
+        <v>98724</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3339,30 +3333,31 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3370,10 +3365,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>776862</v>
+        <v>777013</v>
       </c>
       <c r="R27" t="n">
-        <v>7157681</v>
+        <v>7157601</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3406,6 +3401,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>ca 2 x 2 meter med bladrosetter!</t>
         </is>
       </c>
       <c r="AD27" t="b">
